--- a/artfynd/A 34970-2025 artfynd.xlsx
+++ b/artfynd/A 34970-2025 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130080644</v>
+        <v>130080715</v>
       </c>
       <c r="B8" t="n">
-        <v>4773</v>
+        <v>5197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>352049</v>
+        <v>352047</v>
       </c>
       <c r="R8" t="n">
-        <v>6625465</v>
+        <v>6625255</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130080693</v>
+        <v>130080644</v>
       </c>
       <c r="B9" t="n">
-        <v>101004</v>
+        <v>4773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>351872</v>
+        <v>352049</v>
       </c>
       <c r="R9" t="n">
-        <v>6625323</v>
+        <v>6625465</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130080664</v>
+        <v>130080678</v>
       </c>
       <c r="B10" t="n">
         <v>101004</v>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>352009</v>
+        <v>351989</v>
       </c>
       <c r="R10" t="n">
-        <v>6625188</v>
+        <v>6625211</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130080715</v>
+        <v>130080664</v>
       </c>
       <c r="B11" t="n">
-        <v>5197</v>
+        <v>101004</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>352047</v>
+        <v>352009</v>
       </c>
       <c r="R11" t="n">
-        <v>6625255</v>
+        <v>6625188</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130080678</v>
+        <v>130080693</v>
       </c>
       <c r="B12" t="n">
         <v>101004</v>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>351989</v>
+        <v>351872</v>
       </c>
       <c r="R12" t="n">
-        <v>6625211</v>
+        <v>6625323</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130080665</v>
+        <v>130080742</v>
       </c>
       <c r="B14" t="n">
-        <v>101004</v>
+        <v>5197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>351806</v>
+        <v>352129</v>
       </c>
       <c r="R14" t="n">
-        <v>6625305</v>
+        <v>6625324</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130080742</v>
+        <v>130080665</v>
       </c>
       <c r="B15" t="n">
-        <v>5197</v>
+        <v>101004</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,21 +2064,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>352129</v>
+        <v>351806</v>
       </c>
       <c r="R15" t="n">
-        <v>6625324</v>
+        <v>6625305</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130080733</v>
+        <v>130080650</v>
       </c>
       <c r="B17" t="n">
-        <v>101004</v>
+        <v>8440</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>352048</v>
+        <v>351899</v>
       </c>
       <c r="R17" t="n">
-        <v>6624973</v>
+        <v>6624970</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130080650</v>
+        <v>130080733</v>
       </c>
       <c r="B19" t="n">
-        <v>8440</v>
+        <v>101004</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2512,13 +2512,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>351899</v>
+        <v>352048</v>
       </c>
       <c r="R19" t="n">
-        <v>6624970</v>
+        <v>6624973</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130080697</v>
+        <v>130080704</v>
       </c>
       <c r="B21" t="n">
         <v>101004</v>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>352047</v>
+        <v>352045</v>
       </c>
       <c r="R21" t="n">
-        <v>6625052</v>
+        <v>6625019</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130080704</v>
+        <v>130080697</v>
       </c>
       <c r="B22" t="n">
         <v>101004</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>352045</v>
+        <v>352047</v>
       </c>
       <c r="R22" t="n">
-        <v>6625019</v>
+        <v>6625052</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2901,32 +2901,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130080718</v>
+        <v>130080673</v>
       </c>
       <c r="B23" t="n">
-        <v>92943</v>
+        <v>101004</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>351953</v>
+        <v>351941</v>
       </c>
       <c r="R23" t="n">
-        <v>6625332</v>
+        <v>6625194</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3007,7 +3007,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130080716</v>
+        <v>130080725</v>
       </c>
       <c r="B24" t="n">
         <v>101004</v>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>352027</v>
+        <v>351884</v>
       </c>
       <c r="R24" t="n">
-        <v>6625029</v>
+        <v>6625119</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3113,7 +3113,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130080725</v>
+        <v>130080716</v>
       </c>
       <c r="B25" t="n">
         <v>101004</v>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>351884</v>
+        <v>352027</v>
       </c>
       <c r="R25" t="n">
-        <v>6625119</v>
+        <v>6625029</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3219,32 +3219,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130080673</v>
+        <v>130080718</v>
       </c>
       <c r="B26" t="n">
-        <v>101004</v>
+        <v>92943</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>351941</v>
+        <v>351953</v>
       </c>
       <c r="R26" t="n">
-        <v>6625194</v>
+        <v>6625332</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130080646</v>
+        <v>130080710</v>
       </c>
       <c r="B27" t="n">
-        <v>101004</v>
+        <v>92905</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>351958</v>
+        <v>351943</v>
       </c>
       <c r="R27" t="n">
-        <v>6625185</v>
+        <v>6625324</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130080710</v>
+        <v>130080646</v>
       </c>
       <c r="B28" t="n">
-        <v>92905</v>
+        <v>101004</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>351943</v>
+        <v>351958</v>
       </c>
       <c r="R28" t="n">
-        <v>6625324</v>
+        <v>6625185</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130080729</v>
+        <v>130080734</v>
       </c>
       <c r="B30" t="n">
         <v>101004</v>
@@ -3678,13 +3678,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>351891</v>
+        <v>352092</v>
       </c>
       <c r="R30" t="n">
-        <v>6625317</v>
+        <v>6624985</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130080734</v>
+        <v>130080729</v>
       </c>
       <c r="B31" t="n">
         <v>101004</v>
@@ -3784,13 +3784,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>352092</v>
+        <v>351891</v>
       </c>
       <c r="R31" t="n">
-        <v>6624985</v>
+        <v>6625317</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130080684</v>
+        <v>130080709</v>
       </c>
       <c r="B34" t="n">
-        <v>101004</v>
+        <v>91053</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>352014</v>
+        <v>351843</v>
       </c>
       <c r="R34" t="n">
-        <v>6625206</v>
+        <v>6625177</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130080694</v>
+        <v>130080686</v>
       </c>
       <c r="B35" t="n">
         <v>101004</v>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>352047</v>
+        <v>352054</v>
       </c>
       <c r="R35" t="n">
-        <v>6624983</v>
+        <v>6625054</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130080695</v>
+        <v>130080653</v>
       </c>
       <c r="B36" t="n">
         <v>101004</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>351845</v>
+        <v>351849</v>
       </c>
       <c r="R36" t="n">
-        <v>6625269</v>
+        <v>6625259</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4385,10 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130080709</v>
+        <v>130080695</v>
       </c>
       <c r="B37" t="n">
-        <v>91053</v>
+        <v>101004</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>351843</v>
+        <v>351845</v>
       </c>
       <c r="R37" t="n">
-        <v>6625177</v>
+        <v>6625269</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4491,7 +4491,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130080653</v>
+        <v>130080684</v>
       </c>
       <c r="B38" t="n">
         <v>101004</v>
@@ -4526,10 +4526,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>351849</v>
+        <v>352014</v>
       </c>
       <c r="R38" t="n">
-        <v>6625259</v>
+        <v>6625206</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4597,32 +4597,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130080727</v>
+        <v>130080694</v>
       </c>
       <c r="B39" t="n">
-        <v>92943</v>
+        <v>101004</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4632,13 +4632,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>351974</v>
+        <v>352047</v>
       </c>
       <c r="R39" t="n">
-        <v>6625448</v>
+        <v>6624983</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4703,32 +4703,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130080686</v>
+        <v>130080727</v>
       </c>
       <c r="B40" t="n">
-        <v>101004</v>
+        <v>92943</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4738,13 +4738,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>352054</v>
+        <v>351974</v>
       </c>
       <c r="R40" t="n">
-        <v>6625054</v>
+        <v>6625448</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130080674</v>
+        <v>130080707</v>
       </c>
       <c r="B44" t="n">
         <v>101004</v>
@@ -5162,10 +5162,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>352086</v>
+        <v>351988</v>
       </c>
       <c r="R44" t="n">
-        <v>6624991</v>
+        <v>6625206</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5233,7 +5233,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130080707</v>
+        <v>130080750</v>
       </c>
       <c r="B45" t="n">
         <v>101004</v>
@@ -5262,16 +5262,20 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tostebol 2:1, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>351988</v>
+        <v>352033</v>
       </c>
       <c r="R45" t="n">
-        <v>6625206</v>
+        <v>6625037</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5312,6 +5316,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5339,7 +5344,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130080743</v>
+        <v>130080754</v>
       </c>
       <c r="B46" t="n">
         <v>101004</v>
@@ -5374,10 +5379,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>351863</v>
+        <v>351994</v>
       </c>
       <c r="R46" t="n">
-        <v>6625270</v>
+        <v>6625214</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5445,7 +5450,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130080749</v>
+        <v>130080687</v>
       </c>
       <c r="B47" t="n">
         <v>101004</v>
@@ -5480,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>352067</v>
+        <v>352063</v>
       </c>
       <c r="R47" t="n">
-        <v>6624994</v>
+        <v>6625046</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5551,7 +5556,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130080754</v>
+        <v>130080659</v>
       </c>
       <c r="B48" t="n">
         <v>101004</v>
@@ -5586,10 +5591,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>351994</v>
+        <v>351978</v>
       </c>
       <c r="R48" t="n">
-        <v>6625214</v>
+        <v>6625180</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5657,7 +5662,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130080659</v>
+        <v>130080668</v>
       </c>
       <c r="B49" t="n">
         <v>101004</v>
@@ -5692,10 +5697,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>351978</v>
+        <v>352009</v>
       </c>
       <c r="R49" t="n">
-        <v>6625180</v>
+        <v>6625177</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5763,32 +5768,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130080705</v>
+        <v>130080722</v>
       </c>
       <c r="B50" t="n">
-        <v>92943</v>
+        <v>101004</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5798,13 +5803,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>351964</v>
+        <v>351871</v>
       </c>
       <c r="R50" t="n">
-        <v>6625310</v>
+        <v>6625188</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5869,7 +5874,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130080750</v>
+        <v>130080746</v>
       </c>
       <c r="B51" t="n">
         <v>101004</v>
@@ -5898,20 +5903,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tostebol 2:1, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>352033</v>
+        <v>351961</v>
       </c>
       <c r="R51" t="n">
-        <v>6625037</v>
+        <v>6625364</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5952,7 +5953,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5980,7 +5980,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130080687</v>
+        <v>130080743</v>
       </c>
       <c r="B52" t="n">
         <v>101004</v>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>352063</v>
+        <v>351863</v>
       </c>
       <c r="R52" t="n">
-        <v>6625046</v>
+        <v>6625270</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130080668</v>
+        <v>130080674</v>
       </c>
       <c r="B53" t="n">
         <v>101004</v>
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>352009</v>
+        <v>352086</v>
       </c>
       <c r="R53" t="n">
-        <v>6625177</v>
+        <v>6624991</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6192,7 +6192,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130080746</v>
+        <v>130080749</v>
       </c>
       <c r="B54" t="n">
         <v>101004</v>
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>351961</v>
+        <v>352067</v>
       </c>
       <c r="R54" t="n">
-        <v>6625364</v>
+        <v>6624994</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6404,32 +6404,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130080722</v>
+        <v>130080705</v>
       </c>
       <c r="B56" t="n">
-        <v>101004</v>
+        <v>92943</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6439,13 +6439,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>351871</v>
+        <v>351964</v>
       </c>
       <c r="R56" t="n">
-        <v>6625188</v>
+        <v>6625310</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6510,10 +6510,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130080735</v>
+        <v>130080731</v>
       </c>
       <c r="B57" t="n">
-        <v>101004</v>
+        <v>5197</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>352060</v>
+        <v>352108</v>
       </c>
       <c r="R57" t="n">
-        <v>6624988</v>
+        <v>6625477</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6616,10 +6616,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130080692</v>
+        <v>130080702</v>
       </c>
       <c r="B58" t="n">
-        <v>101004</v>
+        <v>5197</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6627,21 +6627,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>351814</v>
+        <v>352012</v>
       </c>
       <c r="R58" t="n">
-        <v>6625310</v>
+        <v>6625262</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6722,10 +6722,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130080731</v>
+        <v>130080700</v>
       </c>
       <c r="B59" t="n">
-        <v>5197</v>
+        <v>101004</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6733,21 +6733,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>352108</v>
+        <v>351954</v>
       </c>
       <c r="R59" t="n">
-        <v>6625477</v>
+        <v>6625185</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6828,10 +6828,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130080702</v>
+        <v>130080735</v>
       </c>
       <c r="B60" t="n">
-        <v>5197</v>
+        <v>101004</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6839,21 +6839,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>352012</v>
+        <v>352060</v>
       </c>
       <c r="R60" t="n">
-        <v>6625262</v>
+        <v>6624988</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6934,7 +6934,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130080700</v>
+        <v>130080692</v>
       </c>
       <c r="B61" t="n">
         <v>101004</v>
@@ -6969,13 +6969,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>351954</v>
+        <v>351814</v>
       </c>
       <c r="R61" t="n">
-        <v>6625185</v>
+        <v>6625310</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130080648</v>
+        <v>130080661</v>
       </c>
       <c r="B63" t="n">
         <v>101004</v>
@@ -7181,13 +7181,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>351888</v>
+        <v>351899</v>
       </c>
       <c r="R63" t="n">
-        <v>6625110</v>
+        <v>6625315</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130080661</v>
+        <v>130080648</v>
       </c>
       <c r="B64" t="n">
         <v>101004</v>
@@ -7287,13 +7287,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>351899</v>
+        <v>351888</v>
       </c>
       <c r="R64" t="n">
-        <v>6625315</v>
+        <v>6625110</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7358,32 +7358,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130080732</v>
+        <v>130080682</v>
       </c>
       <c r="B65" t="n">
-        <v>92943</v>
+        <v>101004</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7393,10 +7393,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>351949</v>
+        <v>352070</v>
       </c>
       <c r="R65" t="n">
-        <v>6625336</v>
+        <v>6624978</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7464,7 +7464,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130080682</v>
+        <v>130080676</v>
       </c>
       <c r="B66" t="n">
         <v>101004</v>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>352070</v>
+        <v>352034</v>
       </c>
       <c r="R66" t="n">
-        <v>6624978</v>
+        <v>6625020</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7570,32 +7570,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130080676</v>
+        <v>130080732</v>
       </c>
       <c r="B67" t="n">
-        <v>101004</v>
+        <v>92943</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7605,10 +7605,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>352034</v>
+        <v>351949</v>
       </c>
       <c r="R67" t="n">
-        <v>6625020</v>
+        <v>6625336</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7782,32 +7782,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130080658</v>
+        <v>130080688</v>
       </c>
       <c r="B69" t="n">
-        <v>80229</v>
+        <v>92943</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6463</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7817,13 +7817,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>352098</v>
+        <v>351946</v>
       </c>
       <c r="R69" t="n">
-        <v>6625401</v>
+        <v>6625322</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7888,10 +7888,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130080677</v>
+        <v>130080658</v>
       </c>
       <c r="B70" t="n">
-        <v>101004</v>
+        <v>80229</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7899,21 +7899,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>351993</v>
+        <v>352098</v>
       </c>
       <c r="R70" t="n">
-        <v>6625176</v>
+        <v>6625401</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8100,32 +8100,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130080688</v>
+        <v>130080744</v>
       </c>
       <c r="B72" t="n">
-        <v>92943</v>
+        <v>101004</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8135,13 +8135,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>351946</v>
+        <v>352017</v>
       </c>
       <c r="R72" t="n">
-        <v>6625322</v>
+        <v>6625252</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130080744</v>
+        <v>130080677</v>
       </c>
       <c r="B73" t="n">
         <v>101004</v>
@@ -8241,13 +8241,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>352017</v>
+        <v>351993</v>
       </c>
       <c r="R73" t="n">
-        <v>6625252</v>
+        <v>6625176</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130080649</v>
+        <v>130080643</v>
       </c>
       <c r="B74" t="n">
         <v>101004</v>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>351813</v>
+        <v>352061</v>
       </c>
       <c r="R74" t="n">
-        <v>6625308</v>
+        <v>6625058</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8418,7 +8418,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130080680</v>
+        <v>130080649</v>
       </c>
       <c r="B75" t="n">
         <v>101004</v>
@@ -8453,13 +8453,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>351923</v>
+        <v>351813</v>
       </c>
       <c r="R75" t="n">
-        <v>6625280</v>
+        <v>6625308</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130080643</v>
+        <v>130080690</v>
       </c>
       <c r="B76" t="n">
         <v>101004</v>
@@ -8559,13 +8559,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>352061</v>
+        <v>351880</v>
       </c>
       <c r="R76" t="n">
-        <v>6625058</v>
+        <v>6625196</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130080690</v>
+        <v>130080680</v>
       </c>
       <c r="B77" t="n">
         <v>101004</v>
@@ -8665,13 +8665,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>351880</v>
+        <v>351923</v>
       </c>
       <c r="R77" t="n">
-        <v>6625196</v>
+        <v>6625280</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8736,32 +8736,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130080748</v>
+        <v>130080711</v>
       </c>
       <c r="B78" t="n">
-        <v>101004</v>
+        <v>92943</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8771,10 +8771,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>351968</v>
+        <v>351948</v>
       </c>
       <c r="R78" t="n">
-        <v>6625362</v>
+        <v>6625339</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8842,32 +8842,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130080711</v>
+        <v>130080748</v>
       </c>
       <c r="B79" t="n">
-        <v>92943</v>
+        <v>101004</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8877,10 +8877,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>351948</v>
+        <v>351968</v>
       </c>
       <c r="R79" t="n">
-        <v>6625339</v>
+        <v>6625362</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8948,7 +8948,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130080747</v>
+        <v>130080675</v>
       </c>
       <c r="B80" t="n">
         <v>101004</v>
@@ -8983,10 +8983,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>351963</v>
+        <v>352078</v>
       </c>
       <c r="R80" t="n">
-        <v>6625354</v>
+        <v>6624994</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9054,10 +9054,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130080698</v>
+        <v>130080724</v>
       </c>
       <c r="B81" t="n">
-        <v>4773</v>
+        <v>101004</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9065,21 +9065,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9089,10 +9089,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>351986</v>
+        <v>352010</v>
       </c>
       <c r="R81" t="n">
-        <v>6625378</v>
+        <v>6625223</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9160,32 +9160,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130080652</v>
+        <v>130080747</v>
       </c>
       <c r="B82" t="n">
-        <v>92943</v>
+        <v>101004</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>351953</v>
+        <v>351963</v>
       </c>
       <c r="R82" t="n">
-        <v>6625320</v>
+        <v>6625354</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9266,10 +9266,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130080675</v>
+        <v>130080698</v>
       </c>
       <c r="B83" t="n">
-        <v>101004</v>
+        <v>4773</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9277,21 +9277,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>352078</v>
+        <v>351986</v>
       </c>
       <c r="R83" t="n">
-        <v>6624994</v>
+        <v>6625378</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9372,32 +9372,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130080724</v>
+        <v>130080652</v>
       </c>
       <c r="B84" t="n">
-        <v>101004</v>
+        <v>92943</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9407,10 +9407,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>352010</v>
+        <v>351953</v>
       </c>
       <c r="R84" t="n">
-        <v>6625223</v>
+        <v>6625320</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>

--- a/artfynd/A 34970-2025 artfynd.xlsx
+++ b/artfynd/A 34970-2025 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130080681</v>
+        <v>130080679</v>
       </c>
       <c r="B5" t="n">
-        <v>80235</v>
+        <v>8440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>352112</v>
+        <v>351893</v>
       </c>
       <c r="R5" t="n">
-        <v>6625411</v>
+        <v>6624978</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130080679</v>
+        <v>130080681</v>
       </c>
       <c r="B6" t="n">
-        <v>8440</v>
+        <v>80235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>351893</v>
+        <v>352112</v>
       </c>
       <c r="R6" t="n">
-        <v>6624978</v>
+        <v>6625411</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130080689</v>
+        <v>130080703</v>
       </c>
       <c r="B41" t="n">
-        <v>80068</v>
+        <v>40126</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6441</v>
+        <v>214803</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>352000</v>
+        <v>351947</v>
       </c>
       <c r="R41" t="n">
-        <v>6625332</v>
+        <v>6625286</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4915,10 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130080703</v>
+        <v>130080689</v>
       </c>
       <c r="B42" t="n">
-        <v>40126</v>
+        <v>80068</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>214803</v>
+        <v>6441</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>351947</v>
+        <v>352000</v>
       </c>
       <c r="R42" t="n">
-        <v>6625286</v>
+        <v>6625332</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -7782,32 +7782,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130080744</v>
+        <v>130080753</v>
       </c>
       <c r="B69" t="n">
-        <v>101020</v>
+        <v>57738</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7817,13 +7817,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>352017</v>
+        <v>351938</v>
       </c>
       <c r="R69" t="n">
-        <v>6625252</v>
+        <v>6625338</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7888,10 +7888,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130080677</v>
+        <v>130080658</v>
       </c>
       <c r="B70" t="n">
-        <v>101020</v>
+        <v>80235</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7899,21 +7899,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>351993</v>
+        <v>352098</v>
       </c>
       <c r="R70" t="n">
-        <v>6625176</v>
+        <v>6625401</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7994,10 +7994,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130080753</v>
+        <v>130080688</v>
       </c>
       <c r="B71" t="n">
-        <v>57738</v>
+        <v>92959</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8005,21 +8005,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>351938</v>
+        <v>351946</v>
       </c>
       <c r="R71" t="n">
-        <v>6625338</v>
+        <v>6625322</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8100,10 +8100,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130080658</v>
+        <v>130080744</v>
       </c>
       <c r="B72" t="n">
-        <v>80235</v>
+        <v>101020</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8111,21 +8111,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>352098</v>
+        <v>352017</v>
       </c>
       <c r="R72" t="n">
-        <v>6625401</v>
+        <v>6625252</v>
       </c>
       <c r="S72" t="n">
         <v>6</v>
@@ -8206,32 +8206,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130080688</v>
+        <v>130080677</v>
       </c>
       <c r="B73" t="n">
-        <v>92959</v>
+        <v>101020</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>351946</v>
+        <v>351993</v>
       </c>
       <c r="R73" t="n">
-        <v>6625322</v>
+        <v>6625176</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8948,32 +8948,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130080652</v>
+        <v>130080698</v>
       </c>
       <c r="B80" t="n">
-        <v>92959</v>
+        <v>4773</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5966</v>
+        <v>100299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8983,10 +8983,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>351953</v>
+        <v>351986</v>
       </c>
       <c r="R80" t="n">
-        <v>6625320</v>
+        <v>6625378</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9054,32 +9054,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130080675</v>
+        <v>130080652</v>
       </c>
       <c r="B81" t="n">
-        <v>101020</v>
+        <v>92959</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9089,10 +9089,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>352078</v>
+        <v>351953</v>
       </c>
       <c r="R81" t="n">
-        <v>6624994</v>
+        <v>6625320</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9160,7 +9160,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130080747</v>
+        <v>130080675</v>
       </c>
       <c r="B82" t="n">
         <v>101020</v>
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>351963</v>
+        <v>352078</v>
       </c>
       <c r="R82" t="n">
-        <v>6625354</v>
+        <v>6624994</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9266,7 +9266,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130080724</v>
+        <v>130080747</v>
       </c>
       <c r="B83" t="n">
         <v>101020</v>
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>352010</v>
+        <v>351963</v>
       </c>
       <c r="R83" t="n">
-        <v>6625223</v>
+        <v>6625354</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9372,10 +9372,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130080698</v>
+        <v>130080724</v>
       </c>
       <c r="B84" t="n">
-        <v>4773</v>
+        <v>101020</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9383,21 +9383,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9407,10 +9407,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>351986</v>
+        <v>352010</v>
       </c>
       <c r="R84" t="n">
-        <v>6625378</v>
+        <v>6625223</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>

--- a/artfynd/A 34970-2025 artfynd.xlsx
+++ b/artfynd/A 34970-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130080714</v>
+        <v>130080721</v>
       </c>
       <c r="B2" t="n">
-        <v>101020</v>
+        <v>91603</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>352013</v>
+        <v>351857</v>
       </c>
       <c r="R2" t="n">
-        <v>6625233</v>
+        <v>6625260</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130080721</v>
+        <v>130080714</v>
       </c>
       <c r="B3" t="n">
-        <v>91603</v>
+        <v>101020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>351857</v>
+        <v>352013</v>
       </c>
       <c r="R3" t="n">
-        <v>6625260</v>
+        <v>6625233</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130080737</v>
+        <v>130080644</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>4773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>351971</v>
+        <v>352049</v>
       </c>
       <c r="R7" t="n">
-        <v>6625428</v>
+        <v>6625465</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130080644</v>
+        <v>130080737</v>
       </c>
       <c r="B8" t="n">
-        <v>4773</v>
+        <v>79095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>352049</v>
+        <v>351971</v>
       </c>
       <c r="R8" t="n">
-        <v>6625465</v>
+        <v>6625428</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130080665</v>
+        <v>130080742</v>
       </c>
       <c r="B13" t="n">
-        <v>101020</v>
+        <v>5197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>351806</v>
+        <v>352129</v>
       </c>
       <c r="R13" t="n">
-        <v>6625305</v>
+        <v>6625324</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130080730</v>
+        <v>130080672</v>
       </c>
       <c r="B14" t="n">
-        <v>101020</v>
+        <v>8440</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>351959</v>
+        <v>351844</v>
       </c>
       <c r="R14" t="n">
-        <v>6625368</v>
+        <v>6625206</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130080742</v>
+        <v>130080665</v>
       </c>
       <c r="B15" t="n">
-        <v>5197</v>
+        <v>101020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,21 +2064,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>352129</v>
+        <v>351806</v>
       </c>
       <c r="R15" t="n">
-        <v>6625324</v>
+        <v>6625305</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130080672</v>
+        <v>130080730</v>
       </c>
       <c r="B16" t="n">
-        <v>8440</v>
+        <v>101020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2170,21 +2170,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>351844</v>
+        <v>351959</v>
       </c>
       <c r="R16" t="n">
-        <v>6625206</v>
+        <v>6625368</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130080703</v>
+        <v>130080689</v>
       </c>
       <c r="B41" t="n">
-        <v>40126</v>
+        <v>80068</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>214803</v>
+        <v>6441</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>351947</v>
+        <v>352000</v>
       </c>
       <c r="R41" t="n">
-        <v>6625286</v>
+        <v>6625332</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4915,10 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130080689</v>
+        <v>130080703</v>
       </c>
       <c r="B42" t="n">
-        <v>80068</v>
+        <v>40126</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6441</v>
+        <v>214803</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>352000</v>
+        <v>351947</v>
       </c>
       <c r="R42" t="n">
-        <v>6625332</v>
+        <v>6625286</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -7782,32 +7782,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130080753</v>
+        <v>130080744</v>
       </c>
       <c r="B69" t="n">
-        <v>57738</v>
+        <v>101020</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7817,13 +7817,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>351938</v>
+        <v>352017</v>
       </c>
       <c r="R69" t="n">
-        <v>6625338</v>
+        <v>6625252</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7888,10 +7888,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130080658</v>
+        <v>130080677</v>
       </c>
       <c r="B70" t="n">
-        <v>80235</v>
+        <v>101020</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7899,21 +7899,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>352098</v>
+        <v>351993</v>
       </c>
       <c r="R70" t="n">
-        <v>6625401</v>
+        <v>6625176</v>
       </c>
       <c r="S70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7994,10 +7994,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130080688</v>
+        <v>130080753</v>
       </c>
       <c r="B71" t="n">
-        <v>92959</v>
+        <v>57738</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8005,21 +8005,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>351946</v>
+        <v>351938</v>
       </c>
       <c r="R71" t="n">
-        <v>6625322</v>
+        <v>6625338</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8100,10 +8100,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130080744</v>
+        <v>130080658</v>
       </c>
       <c r="B72" t="n">
-        <v>101020</v>
+        <v>80235</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8111,21 +8111,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>352017</v>
+        <v>352098</v>
       </c>
       <c r="R72" t="n">
-        <v>6625252</v>
+        <v>6625401</v>
       </c>
       <c r="S72" t="n">
         <v>6</v>
@@ -8206,32 +8206,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130080677</v>
+        <v>130080688</v>
       </c>
       <c r="B73" t="n">
-        <v>101020</v>
+        <v>92959</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>351993</v>
+        <v>351946</v>
       </c>
       <c r="R73" t="n">
-        <v>6625176</v>
+        <v>6625322</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>

--- a/artfynd/A 34970-2025 artfynd.xlsx
+++ b/artfynd/A 34970-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130080721</v>
       </c>
       <c r="B2" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>130080714</v>
       </c>
       <c r="B3" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>130080708</v>
       </c>
       <c r="B4" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130080715</v>
+        <v>130080693</v>
       </c>
       <c r="B9" t="n">
-        <v>5197</v>
+        <v>101022</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>352047</v>
+        <v>351872</v>
       </c>
       <c r="R9" t="n">
-        <v>6625255</v>
+        <v>6625323</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130080693</v>
+        <v>130080678</v>
       </c>
       <c r="B10" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>351872</v>
+        <v>351989</v>
       </c>
       <c r="R10" t="n">
-        <v>6625323</v>
+        <v>6625211</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130080678</v>
+        <v>130080664</v>
       </c>
       <c r="B11" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>351989</v>
+        <v>352009</v>
       </c>
       <c r="R11" t="n">
-        <v>6625211</v>
+        <v>6625188</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130080664</v>
+        <v>130080715</v>
       </c>
       <c r="B12" t="n">
-        <v>101020</v>
+        <v>5197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>352009</v>
+        <v>352047</v>
       </c>
       <c r="R12" t="n">
-        <v>6625188</v>
+        <v>6625255</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130080742</v>
+        <v>130080672</v>
       </c>
       <c r="B13" t="n">
-        <v>5197</v>
+        <v>8440</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>352129</v>
+        <v>351844</v>
       </c>
       <c r="R13" t="n">
-        <v>6625324</v>
+        <v>6625206</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130080672</v>
+        <v>130080742</v>
       </c>
       <c r="B14" t="n">
-        <v>8440</v>
+        <v>5197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>351844</v>
+        <v>352129</v>
       </c>
       <c r="R14" t="n">
-        <v>6625206</v>
+        <v>6625324</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2056,7 +2056,7 @@
         <v>130080665</v>
       </c>
       <c r="B15" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>130080730</v>
       </c>
       <c r="B16" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>130080691</v>
       </c>
       <c r="B18" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>130080733</v>
       </c>
       <c r="B19" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>130080660</v>
       </c>
       <c r="B20" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,32 +2689,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130080718</v>
+        <v>130080673</v>
       </c>
       <c r="B21" t="n">
-        <v>92959</v>
+        <v>101022</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>351953</v>
+        <v>351941</v>
       </c>
       <c r="R21" t="n">
-        <v>6625332</v>
+        <v>6625194</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130080704</v>
+        <v>130080697</v>
       </c>
       <c r="B22" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>352045</v>
+        <v>352047</v>
       </c>
       <c r="R22" t="n">
-        <v>6625019</v>
+        <v>6625052</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130080697</v>
+        <v>130080716</v>
       </c>
       <c r="B23" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>352047</v>
+        <v>352027</v>
       </c>
       <c r="R23" t="n">
-        <v>6625052</v>
+        <v>6625029</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3007,32 +3007,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130080673</v>
+        <v>130080718</v>
       </c>
       <c r="B24" t="n">
-        <v>101020</v>
+        <v>92961</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>351941</v>
+        <v>351953</v>
       </c>
       <c r="R24" t="n">
-        <v>6625194</v>
+        <v>6625332</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3113,10 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130080725</v>
+        <v>130080704</v>
       </c>
       <c r="B25" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>351884</v>
+        <v>352045</v>
       </c>
       <c r="R25" t="n">
-        <v>6625119</v>
+        <v>6625019</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130080716</v>
+        <v>130080725</v>
       </c>
       <c r="B26" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>352027</v>
+        <v>351884</v>
       </c>
       <c r="R26" t="n">
-        <v>6625029</v>
+        <v>6625119</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3328,7 +3328,7 @@
         <v>130080710</v>
       </c>
       <c r="B27" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>130080646</v>
       </c>
       <c r="B28" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>130080723</v>
       </c>
       <c r="B29" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>130080734</v>
       </c>
       <c r="B30" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>130080729</v>
       </c>
       <c r="B31" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>130080745</v>
       </c>
       <c r="B32" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>130080667</v>
       </c>
       <c r="B33" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>130080709</v>
       </c>
       <c r="B34" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>130080686</v>
       </c>
       <c r="B35" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130080653</v>
+        <v>130080727</v>
       </c>
       <c r="B36" t="n">
-        <v>101020</v>
+        <v>92961</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4314,13 +4314,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>351849</v>
+        <v>351974</v>
       </c>
       <c r="R36" t="n">
-        <v>6625259</v>
+        <v>6625448</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4385,10 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130080695</v>
+        <v>130080653</v>
       </c>
       <c r="B37" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>351845</v>
+        <v>351849</v>
       </c>
       <c r="R37" t="n">
-        <v>6625269</v>
+        <v>6625259</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130080684</v>
+        <v>130080695</v>
       </c>
       <c r="B38" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>352014</v>
+        <v>351845</v>
       </c>
       <c r="R38" t="n">
-        <v>6625206</v>
+        <v>6625269</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130080694</v>
+        <v>130080684</v>
       </c>
       <c r="B39" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>352047</v>
+        <v>352014</v>
       </c>
       <c r="R39" t="n">
-        <v>6624983</v>
+        <v>6625206</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4703,32 +4703,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130080727</v>
+        <v>130080694</v>
       </c>
       <c r="B40" t="n">
-        <v>92959</v>
+        <v>101022</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4738,13 +4738,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>351974</v>
+        <v>352047</v>
       </c>
       <c r="R40" t="n">
-        <v>6625448</v>
+        <v>6624983</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>130080706</v>
       </c>
       <c r="B43" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5127,48 +5127,52 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130080705</v>
+        <v>130080750</v>
       </c>
       <c r="B44" t="n">
-        <v>92959</v>
+        <v>101022</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tostebol 2:1, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>351964</v>
+        <v>352033</v>
       </c>
       <c r="R44" t="n">
-        <v>6625310</v>
+        <v>6625037</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5206,6 +5210,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5233,10 +5238,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130080707</v>
+        <v>130080687</v>
       </c>
       <c r="B45" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5268,10 +5273,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>351988</v>
+        <v>352063</v>
       </c>
       <c r="R45" t="n">
-        <v>6625206</v>
+        <v>6625046</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5339,10 +5344,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130080750</v>
+        <v>130080722</v>
       </c>
       <c r="B46" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5368,20 +5373,16 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tostebol 2:1, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>352033</v>
+        <v>351871</v>
       </c>
       <c r="R46" t="n">
-        <v>6625037</v>
+        <v>6625188</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5422,7 +5423,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5450,10 +5450,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130080754</v>
+        <v>130080707</v>
       </c>
       <c r="B47" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>351994</v>
+        <v>351988</v>
       </c>
       <c r="R47" t="n">
-        <v>6625214</v>
+        <v>6625206</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5556,10 +5556,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130080687</v>
+        <v>130080754</v>
       </c>
       <c r="B48" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>352063</v>
+        <v>351994</v>
       </c>
       <c r="R48" t="n">
-        <v>6625046</v>
+        <v>6625214</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5662,10 +5662,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130080659</v>
+        <v>130080668</v>
       </c>
       <c r="B49" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>351978</v>
+        <v>352009</v>
       </c>
       <c r="R49" t="n">
-        <v>6625180</v>
+        <v>6625177</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5768,10 +5768,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130080668</v>
+        <v>130080746</v>
       </c>
       <c r="B50" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>352009</v>
+        <v>351961</v>
       </c>
       <c r="R50" t="n">
-        <v>6625177</v>
+        <v>6625364</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5874,10 +5874,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130080722</v>
+        <v>130080743</v>
       </c>
       <c r="B51" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5909,10 +5909,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>351871</v>
+        <v>351863</v>
       </c>
       <c r="R51" t="n">
-        <v>6625188</v>
+        <v>6625270</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5980,10 +5980,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130080746</v>
+        <v>130080674</v>
       </c>
       <c r="B52" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>351961</v>
+        <v>352086</v>
       </c>
       <c r="R52" t="n">
-        <v>6625364</v>
+        <v>6624991</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6086,10 +6086,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130080743</v>
+        <v>130080749</v>
       </c>
       <c r="B53" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>351863</v>
+        <v>352067</v>
       </c>
       <c r="R53" t="n">
-        <v>6625270</v>
+        <v>6624994</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6192,32 +6192,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130080674</v>
+        <v>130080705</v>
       </c>
       <c r="B54" t="n">
-        <v>101020</v>
+        <v>92961</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6227,13 +6227,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>352086</v>
+        <v>351964</v>
       </c>
       <c r="R54" t="n">
-        <v>6624991</v>
+        <v>6625310</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6298,10 +6298,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130080749</v>
+        <v>130080659</v>
       </c>
       <c r="B55" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6333,10 +6333,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>352067</v>
+        <v>351978</v>
       </c>
       <c r="R55" t="n">
-        <v>6624994</v>
+        <v>6625180</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6407,7 +6407,7 @@
         <v>130080719</v>
       </c>
       <c r="B56" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>130080700</v>
       </c>
       <c r="B59" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>130080735</v>
       </c>
       <c r="B60" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>130080692</v>
       </c>
       <c r="B61" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>130080661</v>
       </c>
       <c r="B63" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>130080648</v>
       </c>
       <c r="B64" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>130080732</v>
       </c>
       <c r="B65" t="n">
-        <v>92959</v>
+        <v>92961</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130080683</v>
+        <v>130080682</v>
       </c>
       <c r="B66" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>351950</v>
+        <v>352070</v>
       </c>
       <c r="R66" t="n">
-        <v>6624962</v>
+        <v>6624978</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7570,10 +7570,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130080682</v>
+        <v>130080676</v>
       </c>
       <c r="B67" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7605,10 +7605,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>352070</v>
+        <v>352034</v>
       </c>
       <c r="R67" t="n">
-        <v>6624978</v>
+        <v>6625020</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7676,10 +7676,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130080676</v>
+        <v>130080683</v>
       </c>
       <c r="B68" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7711,10 +7711,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>352034</v>
+        <v>351950</v>
       </c>
       <c r="R68" t="n">
-        <v>6625020</v>
+        <v>6624962</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7782,32 +7782,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130080744</v>
+        <v>130080688</v>
       </c>
       <c r="B69" t="n">
-        <v>101020</v>
+        <v>92961</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7817,13 +7817,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>352017</v>
+        <v>351946</v>
       </c>
       <c r="R69" t="n">
-        <v>6625252</v>
+        <v>6625322</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7888,32 +7888,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130080677</v>
+        <v>130080753</v>
       </c>
       <c r="B70" t="n">
-        <v>101020</v>
+        <v>57738</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7923,10 +7923,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>351993</v>
+        <v>351938</v>
       </c>
       <c r="R70" t="n">
-        <v>6625176</v>
+        <v>6625338</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7994,32 +7994,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130080753</v>
+        <v>130080658</v>
       </c>
       <c r="B71" t="n">
-        <v>57738</v>
+        <v>80235</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8029,13 +8029,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>351938</v>
+        <v>352098</v>
       </c>
       <c r="R71" t="n">
-        <v>6625338</v>
+        <v>6625401</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8100,10 +8100,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130080658</v>
+        <v>130080677</v>
       </c>
       <c r="B72" t="n">
-        <v>80235</v>
+        <v>101022</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8111,21 +8111,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8135,13 +8135,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>352098</v>
+        <v>351993</v>
       </c>
       <c r="R72" t="n">
-        <v>6625401</v>
+        <v>6625176</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8206,32 +8206,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130080688</v>
+        <v>130080744</v>
       </c>
       <c r="B73" t="n">
-        <v>92959</v>
+        <v>101022</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8241,13 +8241,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>351946</v>
+        <v>352017</v>
       </c>
       <c r="R73" t="n">
-        <v>6625322</v>
+        <v>6625252</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>130080643</v>
       </c>
       <c r="B74" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8418,10 +8418,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130080649</v>
+        <v>130080680</v>
       </c>
       <c r="B75" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8453,13 +8453,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>351813</v>
+        <v>351923</v>
       </c>
       <c r="R75" t="n">
-        <v>6625308</v>
+        <v>6625280</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8524,10 +8524,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130080690</v>
+        <v>130080649</v>
       </c>
       <c r="B76" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8559,13 +8559,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>351880</v>
+        <v>351813</v>
       </c>
       <c r="R76" t="n">
-        <v>6625196</v>
+        <v>6625308</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8630,10 +8630,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130080680</v>
+        <v>130080690</v>
       </c>
       <c r="B77" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8665,13 +8665,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>351923</v>
+        <v>351880</v>
       </c>
       <c r="R77" t="n">
-        <v>6625280</v>
+        <v>6625196</v>
       </c>
       <c r="S77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8736,32 +8736,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130080711</v>
+        <v>130080748</v>
       </c>
       <c r="B78" t="n">
-        <v>92959</v>
+        <v>101022</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8771,10 +8771,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>351948</v>
+        <v>351968</v>
       </c>
       <c r="R78" t="n">
-        <v>6625339</v>
+        <v>6625362</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8842,32 +8842,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130080748</v>
+        <v>130080711</v>
       </c>
       <c r="B79" t="n">
-        <v>101020</v>
+        <v>92961</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8877,10 +8877,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>351968</v>
+        <v>351948</v>
       </c>
       <c r="R79" t="n">
-        <v>6625362</v>
+        <v>6625339</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9057,7 +9057,7 @@
         <v>130080652</v>
       </c>
       <c r="B81" t="n">
-        <v>92959</v>
+        <v>92961</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>130080675</v>
       </c>
       <c r="B82" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         <v>130080747</v>
       </c>
       <c r="B83" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>130080724</v>
       </c>
       <c r="B84" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 34970-2025 artfynd.xlsx
+++ b/artfynd/A 34970-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130080721</v>
+        <v>130080714</v>
       </c>
       <c r="B2" t="n">
-        <v>91605</v>
+        <v>101109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>351857</v>
+        <v>352013</v>
       </c>
       <c r="R2" t="n">
-        <v>6625260</v>
+        <v>6625233</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130080714</v>
+        <v>130080721</v>
       </c>
       <c r="B3" t="n">
-        <v>101022</v>
+        <v>91692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>352013</v>
+        <v>351857</v>
       </c>
       <c r="R3" t="n">
-        <v>6625233</v>
+        <v>6625260</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -890,7 +890,7 @@
         <v>130080708</v>
       </c>
       <c r="B4" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130080679</v>
+        <v>130080681</v>
       </c>
       <c r="B5" t="n">
-        <v>8440</v>
+        <v>80320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>351893</v>
+        <v>352112</v>
       </c>
       <c r="R5" t="n">
-        <v>6624978</v>
+        <v>6625411</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130080681</v>
+        <v>130080679</v>
       </c>
       <c r="B6" t="n">
-        <v>80235</v>
+        <v>8440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>352112</v>
+        <v>351893</v>
       </c>
       <c r="R6" t="n">
-        <v>6625411</v>
+        <v>6624978</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130080644</v>
+        <v>130080737</v>
       </c>
       <c r="B7" t="n">
-        <v>4773</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>352049</v>
+        <v>351971</v>
       </c>
       <c r="R7" t="n">
-        <v>6625465</v>
+        <v>6625428</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130080737</v>
+        <v>130080644</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>4773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>351971</v>
+        <v>352049</v>
       </c>
       <c r="R8" t="n">
-        <v>6625428</v>
+        <v>6625465</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130080693</v>
+        <v>130080678</v>
       </c>
       <c r="B9" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>351872</v>
+        <v>351989</v>
       </c>
       <c r="R9" t="n">
-        <v>6625323</v>
+        <v>6625211</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130080678</v>
+        <v>130080693</v>
       </c>
       <c r="B10" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>351989</v>
+        <v>351872</v>
       </c>
       <c r="R10" t="n">
-        <v>6625211</v>
+        <v>6625323</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130080664</v>
+        <v>130080715</v>
       </c>
       <c r="B11" t="n">
-        <v>101022</v>
+        <v>5197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>352009</v>
+        <v>352047</v>
       </c>
       <c r="R11" t="n">
-        <v>6625188</v>
+        <v>6625255</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130080715</v>
+        <v>130080664</v>
       </c>
       <c r="B12" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>352047</v>
+        <v>352009</v>
       </c>
       <c r="R12" t="n">
-        <v>6625255</v>
+        <v>6625188</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130080672</v>
+        <v>130080730</v>
       </c>
       <c r="B13" t="n">
-        <v>8440</v>
+        <v>101109</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>351844</v>
+        <v>351959</v>
       </c>
       <c r="R13" t="n">
-        <v>6625206</v>
+        <v>6625368</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2056,7 +2056,7 @@
         <v>130080665</v>
       </c>
       <c r="B15" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130080730</v>
+        <v>130080672</v>
       </c>
       <c r="B16" t="n">
-        <v>101022</v>
+        <v>8440</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2170,21 +2170,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>351959</v>
+        <v>351844</v>
       </c>
       <c r="R16" t="n">
-        <v>6625368</v>
+        <v>6625206</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130080650</v>
+        <v>130080660</v>
       </c>
       <c r="B17" t="n">
-        <v>8440</v>
+        <v>101109</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>351899</v>
+        <v>351973</v>
       </c>
       <c r="R17" t="n">
-        <v>6624970</v>
+        <v>6625359</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130080691</v>
+        <v>130080650</v>
       </c>
       <c r="B18" t="n">
-        <v>101022</v>
+        <v>8440</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,21 +2382,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,13 +2406,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>351862</v>
+        <v>351899</v>
       </c>
       <c r="R18" t="n">
-        <v>6625186</v>
+        <v>6624970</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130080733</v>
+        <v>130080691</v>
       </c>
       <c r="B19" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>352048</v>
+        <v>351862</v>
       </c>
       <c r="R19" t="n">
-        <v>6624973</v>
+        <v>6625186</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130080660</v>
+        <v>130080733</v>
       </c>
       <c r="B20" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>351973</v>
+        <v>352048</v>
       </c>
       <c r="R20" t="n">
-        <v>6625359</v>
+        <v>6624973</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2692,7 +2692,7 @@
         <v>130080673</v>
       </c>
       <c r="B21" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130080697</v>
+        <v>130080704</v>
       </c>
       <c r="B22" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>352047</v>
+        <v>352045</v>
       </c>
       <c r="R22" t="n">
-        <v>6625052</v>
+        <v>6625019</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130080716</v>
+        <v>130080725</v>
       </c>
       <c r="B23" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>352027</v>
+        <v>351884</v>
       </c>
       <c r="R23" t="n">
-        <v>6625029</v>
+        <v>6625119</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3010,7 +3010,7 @@
         <v>130080718</v>
       </c>
       <c r="B24" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3113,10 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130080704</v>
+        <v>130080697</v>
       </c>
       <c r="B25" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>352045</v>
+        <v>352047</v>
       </c>
       <c r="R25" t="n">
-        <v>6625019</v>
+        <v>6625052</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130080725</v>
+        <v>130080716</v>
       </c>
       <c r="B26" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>351884</v>
+        <v>352027</v>
       </c>
       <c r="R26" t="n">
-        <v>6625119</v>
+        <v>6625029</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130080710</v>
+        <v>130080646</v>
       </c>
       <c r="B27" t="n">
-        <v>92923</v>
+        <v>101109</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>351943</v>
+        <v>351958</v>
       </c>
       <c r="R27" t="n">
-        <v>6625324</v>
+        <v>6625185</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130080646</v>
+        <v>130080710</v>
       </c>
       <c r="B28" t="n">
-        <v>101022</v>
+        <v>93010</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>351958</v>
+        <v>351943</v>
       </c>
       <c r="R28" t="n">
-        <v>6625185</v>
+        <v>6625324</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3540,7 +3540,7 @@
         <v>130080723</v>
       </c>
       <c r="B29" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130080734</v>
+        <v>130080729</v>
       </c>
       <c r="B30" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3678,13 +3678,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>352092</v>
+        <v>351891</v>
       </c>
       <c r="R30" t="n">
-        <v>6624985</v>
+        <v>6625317</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3749,10 +3749,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130080729</v>
+        <v>130080734</v>
       </c>
       <c r="B31" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,13 +3784,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>351891</v>
+        <v>352092</v>
       </c>
       <c r="R31" t="n">
-        <v>6625317</v>
+        <v>6624985</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>130080745</v>
       </c>
       <c r="B32" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>130080667</v>
       </c>
       <c r="B33" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130080709</v>
+        <v>130080695</v>
       </c>
       <c r="B34" t="n">
-        <v>91071</v>
+        <v>101109</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>351843</v>
+        <v>351845</v>
       </c>
       <c r="R34" t="n">
-        <v>6625177</v>
+        <v>6625269</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130080686</v>
+        <v>130080684</v>
       </c>
       <c r="B35" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>352054</v>
+        <v>352014</v>
       </c>
       <c r="R35" t="n">
-        <v>6625054</v>
+        <v>6625206</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4282,7 +4282,7 @@
         <v>130080727</v>
       </c>
       <c r="B36" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4385,10 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130080653</v>
+        <v>130080686</v>
       </c>
       <c r="B37" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>351849</v>
+        <v>352054</v>
       </c>
       <c r="R37" t="n">
-        <v>6625259</v>
+        <v>6625054</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130080695</v>
+        <v>130080653</v>
       </c>
       <c r="B38" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>351845</v>
+        <v>351849</v>
       </c>
       <c r="R38" t="n">
-        <v>6625269</v>
+        <v>6625259</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130080684</v>
+        <v>130080694</v>
       </c>
       <c r="B39" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>352014</v>
+        <v>352047</v>
       </c>
       <c r="R39" t="n">
-        <v>6625206</v>
+        <v>6624983</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4703,10 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130080694</v>
+        <v>130080709</v>
       </c>
       <c r="B40" t="n">
-        <v>101022</v>
+        <v>91158</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4714,21 +4714,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4738,10 +4738,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>352047</v>
+        <v>351843</v>
       </c>
       <c r="R40" t="n">
-        <v>6624983</v>
+        <v>6625177</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130080689</v>
+        <v>130080703</v>
       </c>
       <c r="B41" t="n">
-        <v>80068</v>
+        <v>40211</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6441</v>
+        <v>214803</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>352000</v>
+        <v>351947</v>
       </c>
       <c r="R41" t="n">
-        <v>6625332</v>
+        <v>6625286</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4915,10 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130080703</v>
+        <v>130080689</v>
       </c>
       <c r="B42" t="n">
-        <v>40126</v>
+        <v>80153</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>214803</v>
+        <v>6441</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>351947</v>
+        <v>352000</v>
       </c>
       <c r="R42" t="n">
-        <v>6625286</v>
+        <v>6625332</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5024,7 +5024,7 @@
         <v>130080706</v>
       </c>
       <c r="B43" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>130080750</v>
       </c>
       <c r="B44" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5238,10 +5238,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130080687</v>
+        <v>130080754</v>
       </c>
       <c r="B45" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>352063</v>
+        <v>351994</v>
       </c>
       <c r="R45" t="n">
-        <v>6625046</v>
+        <v>6625214</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5344,10 +5344,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130080722</v>
+        <v>130080687</v>
       </c>
       <c r="B46" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>351871</v>
+        <v>352063</v>
       </c>
       <c r="R46" t="n">
-        <v>6625188</v>
+        <v>6625046</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5450,10 +5450,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130080707</v>
+        <v>130080743</v>
       </c>
       <c r="B47" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>351988</v>
+        <v>351863</v>
       </c>
       <c r="R47" t="n">
-        <v>6625206</v>
+        <v>6625270</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5556,10 +5556,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130080754</v>
+        <v>130080674</v>
       </c>
       <c r="B48" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>351994</v>
+        <v>352086</v>
       </c>
       <c r="R48" t="n">
-        <v>6625214</v>
+        <v>6624991</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5662,10 +5662,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130080668</v>
+        <v>130080749</v>
       </c>
       <c r="B49" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>352009</v>
+        <v>352067</v>
       </c>
       <c r="R49" t="n">
-        <v>6625177</v>
+        <v>6624994</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5768,10 +5768,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130080746</v>
+        <v>130080719</v>
       </c>
       <c r="B50" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>351961</v>
+        <v>351983</v>
       </c>
       <c r="R50" t="n">
-        <v>6625364</v>
+        <v>6625356</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5874,32 +5874,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130080743</v>
+        <v>130080705</v>
       </c>
       <c r="B51" t="n">
-        <v>101022</v>
+        <v>93048</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5909,13 +5909,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>351863</v>
+        <v>351964</v>
       </c>
       <c r="R51" t="n">
-        <v>6625270</v>
+        <v>6625310</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5980,10 +5980,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130080674</v>
+        <v>130080668</v>
       </c>
       <c r="B52" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>352086</v>
+        <v>352009</v>
       </c>
       <c r="R52" t="n">
-        <v>6624991</v>
+        <v>6625177</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6086,10 +6086,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130080749</v>
+        <v>130080707</v>
       </c>
       <c r="B53" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>352067</v>
+        <v>351988</v>
       </c>
       <c r="R53" t="n">
-        <v>6624994</v>
+        <v>6625206</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6192,32 +6192,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130080705</v>
+        <v>130080659</v>
       </c>
       <c r="B54" t="n">
-        <v>92961</v>
+        <v>101109</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6227,13 +6227,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>351964</v>
+        <v>351978</v>
       </c>
       <c r="R54" t="n">
-        <v>6625310</v>
+        <v>6625180</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6298,10 +6298,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130080659</v>
+        <v>130080722</v>
       </c>
       <c r="B55" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6333,10 +6333,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>351978</v>
+        <v>351871</v>
       </c>
       <c r="R55" t="n">
-        <v>6625180</v>
+        <v>6625188</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6404,10 +6404,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130080719</v>
+        <v>130080746</v>
       </c>
       <c r="B56" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>351983</v>
+        <v>351961</v>
       </c>
       <c r="R56" t="n">
-        <v>6625356</v>
+        <v>6625364</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6510,10 +6510,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130080731</v>
+        <v>130080700</v>
       </c>
       <c r="B57" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6545,13 +6545,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>352108</v>
+        <v>351954</v>
       </c>
       <c r="R57" t="n">
-        <v>6625477</v>
+        <v>6625185</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130080702</v>
+        <v>130080731</v>
       </c>
       <c r="B58" t="n">
         <v>5197</v>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>352012</v>
+        <v>352108</v>
       </c>
       <c r="R58" t="n">
-        <v>6625262</v>
+        <v>6625477</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6722,10 +6722,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130080700</v>
+        <v>130080702</v>
       </c>
       <c r="B59" t="n">
-        <v>101022</v>
+        <v>5197</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6733,21 +6733,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>351954</v>
+        <v>352012</v>
       </c>
       <c r="R59" t="n">
-        <v>6625185</v>
+        <v>6625262</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>130080735</v>
       </c>
       <c r="B60" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>130080692</v>
       </c>
       <c r="B61" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130080720</v>
+        <v>130080661</v>
       </c>
       <c r="B62" t="n">
-        <v>56934</v>
+        <v>101109</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7051,21 +7051,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102613</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7075,13 +7075,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>352012</v>
+        <v>351899</v>
       </c>
       <c r="R62" t="n">
-        <v>6625216</v>
+        <v>6625315</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7146,10 +7146,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130080661</v>
+        <v>130080648</v>
       </c>
       <c r="B63" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7181,13 +7181,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>351899</v>
+        <v>351888</v>
       </c>
       <c r="R63" t="n">
-        <v>6625315</v>
+        <v>6625110</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7252,10 +7252,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130080648</v>
+        <v>130080720</v>
       </c>
       <c r="B64" t="n">
-        <v>101022</v>
+        <v>57019</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7263,21 +7263,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>102613</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7287,10 +7287,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>351888</v>
+        <v>352012</v>
       </c>
       <c r="R64" t="n">
-        <v>6625110</v>
+        <v>6625216</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7358,32 +7358,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130080732</v>
+        <v>130080682</v>
       </c>
       <c r="B65" t="n">
-        <v>92961</v>
+        <v>101109</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7393,10 +7393,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>351949</v>
+        <v>352070</v>
       </c>
       <c r="R65" t="n">
-        <v>6625336</v>
+        <v>6624978</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130080682</v>
+        <v>130080683</v>
       </c>
       <c r="B66" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>352070</v>
+        <v>351950</v>
       </c>
       <c r="R66" t="n">
-        <v>6624978</v>
+        <v>6624962</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7573,7 +7573,7 @@
         <v>130080676</v>
       </c>
       <c r="B67" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7676,32 +7676,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130080683</v>
+        <v>130080732</v>
       </c>
       <c r="B68" t="n">
-        <v>101022</v>
+        <v>93048</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7711,10 +7711,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>351950</v>
+        <v>351949</v>
       </c>
       <c r="R68" t="n">
-        <v>6624962</v>
+        <v>6625336</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7782,32 +7782,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130080688</v>
+        <v>130080677</v>
       </c>
       <c r="B69" t="n">
-        <v>92961</v>
+        <v>101109</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>351946</v>
+        <v>351993</v>
       </c>
       <c r="R69" t="n">
-        <v>6625322</v>
+        <v>6625176</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7888,32 +7888,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130080753</v>
+        <v>130080744</v>
       </c>
       <c r="B70" t="n">
-        <v>57738</v>
+        <v>101109</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>351938</v>
+        <v>352017</v>
       </c>
       <c r="R70" t="n">
-        <v>6625338</v>
+        <v>6625252</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7994,32 +7994,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130080658</v>
+        <v>130080753</v>
       </c>
       <c r="B71" t="n">
-        <v>80235</v>
+        <v>57823</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8029,13 +8029,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>352098</v>
+        <v>351938</v>
       </c>
       <c r="R71" t="n">
-        <v>6625401</v>
+        <v>6625338</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8100,32 +8100,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130080677</v>
+        <v>130080688</v>
       </c>
       <c r="B72" t="n">
-        <v>101022</v>
+        <v>93048</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>351993</v>
+        <v>351946</v>
       </c>
       <c r="R72" t="n">
-        <v>6625176</v>
+        <v>6625322</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8206,10 +8206,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130080744</v>
+        <v>130080658</v>
       </c>
       <c r="B73" t="n">
-        <v>101022</v>
+        <v>80320</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8217,21 +8217,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>352017</v>
+        <v>352098</v>
       </c>
       <c r="R73" t="n">
-        <v>6625252</v>
+        <v>6625401</v>
       </c>
       <c r="S73" t="n">
         <v>6</v>
@@ -8315,7 +8315,7 @@
         <v>130080643</v>
       </c>
       <c r="B74" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>130080680</v>
       </c>
       <c r="B75" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>130080649</v>
       </c>
       <c r="B76" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>130080690</v>
       </c>
       <c r="B77" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8736,32 +8736,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130080748</v>
+        <v>130080711</v>
       </c>
       <c r="B78" t="n">
-        <v>101022</v>
+        <v>93048</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8771,10 +8771,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>351968</v>
+        <v>351948</v>
       </c>
       <c r="R78" t="n">
-        <v>6625362</v>
+        <v>6625339</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8842,32 +8842,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130080711</v>
+        <v>130080748</v>
       </c>
       <c r="B79" t="n">
-        <v>92961</v>
+        <v>101109</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8877,10 +8877,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>351948</v>
+        <v>351968</v>
       </c>
       <c r="R79" t="n">
-        <v>6625339</v>
+        <v>6625362</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8948,32 +8948,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130080698</v>
+        <v>130080652</v>
       </c>
       <c r="B80" t="n">
-        <v>4773</v>
+        <v>93048</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100299</v>
+        <v>5966</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8983,10 +8983,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>351986</v>
+        <v>351953</v>
       </c>
       <c r="R80" t="n">
-        <v>6625378</v>
+        <v>6625320</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9054,32 +9054,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130080652</v>
+        <v>130080747</v>
       </c>
       <c r="B81" t="n">
-        <v>92961</v>
+        <v>101109</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9089,10 +9089,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>351953</v>
+        <v>351963</v>
       </c>
       <c r="R81" t="n">
-        <v>6625320</v>
+        <v>6625354</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9160,10 +9160,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130080675</v>
+        <v>130080724</v>
       </c>
       <c r="B82" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>352078</v>
+        <v>352010</v>
       </c>
       <c r="R82" t="n">
-        <v>6624994</v>
+        <v>6625223</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9266,10 +9266,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130080747</v>
+        <v>130080698</v>
       </c>
       <c r="B83" t="n">
-        <v>101022</v>
+        <v>4773</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9277,21 +9277,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>351963</v>
+        <v>351986</v>
       </c>
       <c r="R83" t="n">
-        <v>6625354</v>
+        <v>6625378</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9372,10 +9372,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130080724</v>
+        <v>130080675</v>
       </c>
       <c r="B84" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9407,10 +9407,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>352010</v>
+        <v>352078</v>
       </c>
       <c r="R84" t="n">
-        <v>6625223</v>
+        <v>6624994</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>

--- a/artfynd/A 34970-2025 artfynd.xlsx
+++ b/artfynd/A 34970-2025 artfynd.xlsx
@@ -2689,32 +2689,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130080673</v>
+        <v>130080718</v>
       </c>
       <c r="B21" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>351941</v>
+        <v>351953</v>
       </c>
       <c r="R21" t="n">
-        <v>6625194</v>
+        <v>6625332</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130080704</v>
+        <v>130080673</v>
       </c>
       <c r="B22" t="n">
         <v>101109</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>352045</v>
+        <v>351941</v>
       </c>
       <c r="R22" t="n">
-        <v>6625019</v>
+        <v>6625194</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2901,7 +2901,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130080725</v>
+        <v>130080716</v>
       </c>
       <c r="B23" t="n">
         <v>101109</v>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>351884</v>
+        <v>352027</v>
       </c>
       <c r="R23" t="n">
-        <v>6625119</v>
+        <v>6625029</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3007,32 +3007,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130080718</v>
+        <v>130080697</v>
       </c>
       <c r="B24" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>351953</v>
+        <v>352047</v>
       </c>
       <c r="R24" t="n">
-        <v>6625332</v>
+        <v>6625052</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3113,7 +3113,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130080697</v>
+        <v>130080704</v>
       </c>
       <c r="B25" t="n">
         <v>101109</v>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>352047</v>
+        <v>352045</v>
       </c>
       <c r="R25" t="n">
-        <v>6625052</v>
+        <v>6625019</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130080716</v>
+        <v>130080725</v>
       </c>
       <c r="B26" t="n">
         <v>101109</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>352027</v>
+        <v>351884</v>
       </c>
       <c r="R26" t="n">
-        <v>6625029</v>
+        <v>6625119</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3325,7 +3325,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130080646</v>
+        <v>130080723</v>
       </c>
       <c r="B27" t="n">
         <v>101109</v>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>351958</v>
+        <v>352039</v>
       </c>
       <c r="R27" t="n">
-        <v>6625185</v>
+        <v>6624980</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130080710</v>
+        <v>130080646</v>
       </c>
       <c r="B28" t="n">
-        <v>93010</v>
+        <v>101109</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>351943</v>
+        <v>351958</v>
       </c>
       <c r="R28" t="n">
-        <v>6625324</v>
+        <v>6625185</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130080723</v>
+        <v>130080710</v>
       </c>
       <c r="B29" t="n">
-        <v>101109</v>
+        <v>93010</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>352039</v>
+        <v>351943</v>
       </c>
       <c r="R29" t="n">
-        <v>6624980</v>
+        <v>6625324</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>

--- a/artfynd/A 34970-2025 artfynd.xlsx
+++ b/artfynd/A 34970-2025 artfynd.xlsx
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130080660</v>
+        <v>130080691</v>
       </c>
       <c r="B17" t="n">
         <v>101109</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>351973</v>
+        <v>351862</v>
       </c>
       <c r="R17" t="n">
-        <v>6625359</v>
+        <v>6625186</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130080650</v>
+        <v>130080733</v>
       </c>
       <c r="B18" t="n">
-        <v>8440</v>
+        <v>101109</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,21 +2382,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,13 +2406,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>351899</v>
+        <v>352048</v>
       </c>
       <c r="R18" t="n">
-        <v>6624970</v>
+        <v>6624973</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130080691</v>
+        <v>130080660</v>
       </c>
       <c r="B19" t="n">
         <v>101109</v>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>351862</v>
+        <v>351973</v>
       </c>
       <c r="R19" t="n">
-        <v>6625186</v>
+        <v>6625359</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130080733</v>
+        <v>130080650</v>
       </c>
       <c r="B20" t="n">
-        <v>101109</v>
+        <v>8440</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2618,13 +2618,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>352048</v>
+        <v>351899</v>
       </c>
       <c r="R20" t="n">
-        <v>6624973</v>
+        <v>6624970</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130080723</v>
+        <v>130080646</v>
       </c>
       <c r="B27" t="n">
         <v>101109</v>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>352039</v>
+        <v>351958</v>
       </c>
       <c r="R27" t="n">
-        <v>6624980</v>
+        <v>6625185</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130080646</v>
+        <v>130080710</v>
       </c>
       <c r="B28" t="n">
-        <v>101109</v>
+        <v>93010</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>351958</v>
+        <v>351943</v>
       </c>
       <c r="R28" t="n">
-        <v>6625185</v>
+        <v>6625324</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130080710</v>
+        <v>130080723</v>
       </c>
       <c r="B29" t="n">
-        <v>93010</v>
+        <v>101109</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>351943</v>
+        <v>352039</v>
       </c>
       <c r="R29" t="n">
-        <v>6625324</v>
+        <v>6624980</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130080695</v>
+        <v>130080709</v>
       </c>
       <c r="B34" t="n">
-        <v>101109</v>
+        <v>91158</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>351845</v>
+        <v>351843</v>
       </c>
       <c r="R34" t="n">
-        <v>6625269</v>
+        <v>6625177</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4173,32 +4173,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130080684</v>
+        <v>130080727</v>
       </c>
       <c r="B35" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>352014</v>
+        <v>351974</v>
       </c>
       <c r="R35" t="n">
-        <v>6625206</v>
+        <v>6625448</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130080727</v>
+        <v>130080695</v>
       </c>
       <c r="B36" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4314,13 +4314,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>351974</v>
+        <v>351845</v>
       </c>
       <c r="R36" t="n">
-        <v>6625448</v>
+        <v>6625269</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130080686</v>
+        <v>130080684</v>
       </c>
       <c r="B37" t="n">
         <v>101109</v>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>352054</v>
+        <v>352014</v>
       </c>
       <c r="R37" t="n">
-        <v>6625054</v>
+        <v>6625206</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4491,7 +4491,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130080653</v>
+        <v>130080686</v>
       </c>
       <c r="B38" t="n">
         <v>101109</v>
@@ -4526,10 +4526,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>351849</v>
+        <v>352054</v>
       </c>
       <c r="R38" t="n">
-        <v>6625259</v>
+        <v>6625054</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4597,7 +4597,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130080694</v>
+        <v>130080653</v>
       </c>
       <c r="B39" t="n">
         <v>101109</v>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>352047</v>
+        <v>351849</v>
       </c>
       <c r="R39" t="n">
-        <v>6624983</v>
+        <v>6625259</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4703,10 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130080709</v>
+        <v>130080694</v>
       </c>
       <c r="B40" t="n">
-        <v>91158</v>
+        <v>101109</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4714,21 +4714,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4738,10 +4738,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>351843</v>
+        <v>352047</v>
       </c>
       <c r="R40" t="n">
-        <v>6625177</v>
+        <v>6624983</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130080703</v>
+        <v>130080706</v>
       </c>
       <c r="B41" t="n">
-        <v>40211</v>
+        <v>101109</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>214803</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>351947</v>
+        <v>351862</v>
       </c>
       <c r="R41" t="n">
-        <v>6625286</v>
+        <v>6625305</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4915,10 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130080689</v>
+        <v>130080703</v>
       </c>
       <c r="B42" t="n">
-        <v>80153</v>
+        <v>40211</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6441</v>
+        <v>214803</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>352000</v>
+        <v>351947</v>
       </c>
       <c r="R42" t="n">
-        <v>6625332</v>
+        <v>6625286</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5021,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130080706</v>
+        <v>130080689</v>
       </c>
       <c r="B43" t="n">
-        <v>101109</v>
+        <v>80153</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>6441</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>351862</v>
+        <v>352000</v>
       </c>
       <c r="R43" t="n">
-        <v>6625305</v>
+        <v>6625332</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5127,7 +5127,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130080750</v>
+        <v>130080707</v>
       </c>
       <c r="B44" t="n">
         <v>101109</v>
@@ -5156,20 +5156,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tostebol 2:1, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>352033</v>
+        <v>351988</v>
       </c>
       <c r="R44" t="n">
-        <v>6625037</v>
+        <v>6625206</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5210,7 +5206,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5238,7 +5233,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130080754</v>
+        <v>130080659</v>
       </c>
       <c r="B45" t="n">
         <v>101109</v>
@@ -5273,10 +5268,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>351994</v>
+        <v>351978</v>
       </c>
       <c r="R45" t="n">
-        <v>6625214</v>
+        <v>6625180</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5344,7 +5339,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130080687</v>
+        <v>130080722</v>
       </c>
       <c r="B46" t="n">
         <v>101109</v>
@@ -5379,10 +5374,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>352063</v>
+        <v>351871</v>
       </c>
       <c r="R46" t="n">
-        <v>6625046</v>
+        <v>6625188</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5450,7 +5445,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130080743</v>
+        <v>130080746</v>
       </c>
       <c r="B47" t="n">
         <v>101109</v>
@@ -5485,10 +5480,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>351863</v>
+        <v>351961</v>
       </c>
       <c r="R47" t="n">
-        <v>6625270</v>
+        <v>6625364</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5556,7 +5551,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130080674</v>
+        <v>130080750</v>
       </c>
       <c r="B48" t="n">
         <v>101109</v>
@@ -5585,16 +5580,20 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tostebol 2:1, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>352086</v>
+        <v>352033</v>
       </c>
       <c r="R48" t="n">
-        <v>6624991</v>
+        <v>6625037</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5635,6 +5634,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5662,7 +5662,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130080749</v>
+        <v>130080754</v>
       </c>
       <c r="B49" t="n">
         <v>101109</v>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>352067</v>
+        <v>351994</v>
       </c>
       <c r="R49" t="n">
-        <v>6624994</v>
+        <v>6625214</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5768,7 +5768,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130080719</v>
+        <v>130080687</v>
       </c>
       <c r="B50" t="n">
         <v>101109</v>
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>351983</v>
+        <v>352063</v>
       </c>
       <c r="R50" t="n">
-        <v>6625356</v>
+        <v>6625046</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5874,32 +5874,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130080705</v>
+        <v>130080743</v>
       </c>
       <c r="B51" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5909,13 +5909,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>351964</v>
+        <v>351863</v>
       </c>
       <c r="R51" t="n">
-        <v>6625310</v>
+        <v>6625270</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130080668</v>
+        <v>130080674</v>
       </c>
       <c r="B52" t="n">
         <v>101109</v>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>352009</v>
+        <v>352086</v>
       </c>
       <c r="R52" t="n">
-        <v>6625177</v>
+        <v>6624991</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130080707</v>
+        <v>130080749</v>
       </c>
       <c r="B53" t="n">
         <v>101109</v>
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>351988</v>
+        <v>352067</v>
       </c>
       <c r="R53" t="n">
-        <v>6625206</v>
+        <v>6624994</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6192,7 +6192,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130080659</v>
+        <v>130080719</v>
       </c>
       <c r="B54" t="n">
         <v>101109</v>
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>351978</v>
+        <v>351983</v>
       </c>
       <c r="R54" t="n">
-        <v>6625180</v>
+        <v>6625356</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6298,32 +6298,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130080722</v>
+        <v>130080705</v>
       </c>
       <c r="B55" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6333,13 +6333,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>351871</v>
+        <v>351964</v>
       </c>
       <c r="R55" t="n">
-        <v>6625188</v>
+        <v>6625310</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130080746</v>
+        <v>130080668</v>
       </c>
       <c r="B56" t="n">
         <v>101109</v>
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>351961</v>
+        <v>352009</v>
       </c>
       <c r="R56" t="n">
-        <v>6625364</v>
+        <v>6625177</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6510,7 +6510,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130080700</v>
+        <v>130080735</v>
       </c>
       <c r="B57" t="n">
         <v>101109</v>
@@ -6545,13 +6545,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>351954</v>
+        <v>352060</v>
       </c>
       <c r="R57" t="n">
-        <v>6625185</v>
+        <v>6624988</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6616,10 +6616,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130080731</v>
+        <v>130080692</v>
       </c>
       <c r="B58" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6627,21 +6627,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>352108</v>
+        <v>351814</v>
       </c>
       <c r="R58" t="n">
-        <v>6625477</v>
+        <v>6625310</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6722,10 +6722,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130080702</v>
+        <v>130080700</v>
       </c>
       <c r="B59" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6733,21 +6733,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>352012</v>
+        <v>351954</v>
       </c>
       <c r="R59" t="n">
-        <v>6625262</v>
+        <v>6625185</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6828,10 +6828,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130080735</v>
+        <v>130080731</v>
       </c>
       <c r="B60" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6839,21 +6839,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>352060</v>
+        <v>352108</v>
       </c>
       <c r="R60" t="n">
-        <v>6624988</v>
+        <v>6625477</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6934,10 +6934,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130080692</v>
+        <v>130080702</v>
       </c>
       <c r="B61" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6945,21 +6945,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6969,10 +6969,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>351814</v>
+        <v>352012</v>
       </c>
       <c r="R61" t="n">
-        <v>6625310</v>
+        <v>6625262</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7358,7 +7358,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130080682</v>
+        <v>130080683</v>
       </c>
       <c r="B65" t="n">
         <v>101109</v>
@@ -7393,10 +7393,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>352070</v>
+        <v>351950</v>
       </c>
       <c r="R65" t="n">
-        <v>6624978</v>
+        <v>6624962</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7464,7 +7464,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130080683</v>
+        <v>130080676</v>
       </c>
       <c r="B66" t="n">
         <v>101109</v>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>351950</v>
+        <v>352034</v>
       </c>
       <c r="R66" t="n">
-        <v>6624962</v>
+        <v>6625020</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7570,32 +7570,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130080676</v>
+        <v>130080732</v>
       </c>
       <c r="B67" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7605,10 +7605,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>352034</v>
+        <v>351949</v>
       </c>
       <c r="R67" t="n">
-        <v>6625020</v>
+        <v>6625336</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7676,32 +7676,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130080732</v>
+        <v>130080682</v>
       </c>
       <c r="B68" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7711,10 +7711,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>351949</v>
+        <v>352070</v>
       </c>
       <c r="R68" t="n">
-        <v>6625336</v>
+        <v>6624978</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8948,32 +8948,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130080652</v>
+        <v>130080675</v>
       </c>
       <c r="B80" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8983,10 +8983,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>351953</v>
+        <v>352078</v>
       </c>
       <c r="R80" t="n">
-        <v>6625320</v>
+        <v>6624994</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9054,7 +9054,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130080747</v>
+        <v>130080724</v>
       </c>
       <c r="B81" t="n">
         <v>101109</v>
@@ -9089,10 +9089,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>351963</v>
+        <v>352010</v>
       </c>
       <c r="R81" t="n">
-        <v>6625354</v>
+        <v>6625223</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9160,32 +9160,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130080724</v>
+        <v>130080652</v>
       </c>
       <c r="B82" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>352010</v>
+        <v>351953</v>
       </c>
       <c r="R82" t="n">
-        <v>6625223</v>
+        <v>6625320</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9266,10 +9266,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130080698</v>
+        <v>130080747</v>
       </c>
       <c r="B83" t="n">
-        <v>4773</v>
+        <v>101109</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9277,21 +9277,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>351986</v>
+        <v>351963</v>
       </c>
       <c r="R83" t="n">
-        <v>6625378</v>
+        <v>6625354</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9372,10 +9372,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130080675</v>
+        <v>130080698</v>
       </c>
       <c r="B84" t="n">
-        <v>101109</v>
+        <v>4773</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9383,21 +9383,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9407,10 +9407,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>352078</v>
+        <v>351986</v>
       </c>
       <c r="R84" t="n">
-        <v>6624994</v>
+        <v>6625378</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>

--- a/artfynd/A 34970-2025 artfynd.xlsx
+++ b/artfynd/A 34970-2025 artfynd.xlsx
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130080678</v>
+        <v>130080715</v>
       </c>
       <c r="B9" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>351989</v>
+        <v>352047</v>
       </c>
       <c r="R9" t="n">
-        <v>6625211</v>
+        <v>6625255</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130080715</v>
+        <v>130080678</v>
       </c>
       <c r="B11" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>352047</v>
+        <v>351989</v>
       </c>
       <c r="R11" t="n">
-        <v>6625255</v>
+        <v>6625211</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130080730</v>
+        <v>130080742</v>
       </c>
       <c r="B13" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>351959</v>
+        <v>352129</v>
       </c>
       <c r="R13" t="n">
-        <v>6625368</v>
+        <v>6625324</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130080742</v>
+        <v>130080672</v>
       </c>
       <c r="B14" t="n">
-        <v>5197</v>
+        <v>8440</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>352129</v>
+        <v>351844</v>
       </c>
       <c r="R14" t="n">
-        <v>6625324</v>
+        <v>6625206</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130080672</v>
+        <v>130080730</v>
       </c>
       <c r="B16" t="n">
-        <v>8440</v>
+        <v>101109</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2170,21 +2170,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>351844</v>
+        <v>351959</v>
       </c>
       <c r="R16" t="n">
-        <v>6625206</v>
+        <v>6625368</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130080691</v>
+        <v>130080650</v>
       </c>
       <c r="B17" t="n">
-        <v>101109</v>
+        <v>8440</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>351862</v>
+        <v>351899</v>
       </c>
       <c r="R17" t="n">
-        <v>6625186</v>
+        <v>6624970</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130080733</v>
+        <v>130080691</v>
       </c>
       <c r="B18" t="n">
         <v>101109</v>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>352048</v>
+        <v>351862</v>
       </c>
       <c r="R18" t="n">
-        <v>6624973</v>
+        <v>6625186</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130080660</v>
+        <v>130080733</v>
       </c>
       <c r="B19" t="n">
         <v>101109</v>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>351973</v>
+        <v>352048</v>
       </c>
       <c r="R19" t="n">
-        <v>6625359</v>
+        <v>6624973</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130080650</v>
+        <v>130080660</v>
       </c>
       <c r="B20" t="n">
-        <v>8440</v>
+        <v>101109</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2618,13 +2618,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>351899</v>
+        <v>351973</v>
       </c>
       <c r="R20" t="n">
-        <v>6624970</v>
+        <v>6625359</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2689,32 +2689,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130080718</v>
+        <v>130080704</v>
       </c>
       <c r="B21" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>351953</v>
+        <v>352045</v>
       </c>
       <c r="R21" t="n">
-        <v>6625332</v>
+        <v>6625019</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130080673</v>
+        <v>130080697</v>
       </c>
       <c r="B22" t="n">
         <v>101109</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>351941</v>
+        <v>352047</v>
       </c>
       <c r="R22" t="n">
-        <v>6625194</v>
+        <v>6625052</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2901,7 +2901,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130080716</v>
+        <v>130080673</v>
       </c>
       <c r="B23" t="n">
         <v>101109</v>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>352027</v>
+        <v>351941</v>
       </c>
       <c r="R23" t="n">
-        <v>6625029</v>
+        <v>6625194</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3007,7 +3007,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130080697</v>
+        <v>130080725</v>
       </c>
       <c r="B24" t="n">
         <v>101109</v>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>352047</v>
+        <v>351884</v>
       </c>
       <c r="R24" t="n">
-        <v>6625052</v>
+        <v>6625119</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3113,7 +3113,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130080704</v>
+        <v>130080716</v>
       </c>
       <c r="B25" t="n">
         <v>101109</v>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>352045</v>
+        <v>352027</v>
       </c>
       <c r="R25" t="n">
-        <v>6625019</v>
+        <v>6625029</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3219,32 +3219,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130080725</v>
+        <v>130080718</v>
       </c>
       <c r="B26" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>351884</v>
+        <v>351953</v>
       </c>
       <c r="R26" t="n">
-        <v>6625119</v>
+        <v>6625332</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130080646</v>
+        <v>130080710</v>
       </c>
       <c r="B27" t="n">
-        <v>101109</v>
+        <v>93010</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>351958</v>
+        <v>351943</v>
       </c>
       <c r="R27" t="n">
-        <v>6625185</v>
+        <v>6625324</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130080710</v>
+        <v>130080646</v>
       </c>
       <c r="B28" t="n">
-        <v>93010</v>
+        <v>101109</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>351943</v>
+        <v>351958</v>
       </c>
       <c r="R28" t="n">
-        <v>6625324</v>
+        <v>6625185</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130080729</v>
+        <v>130080734</v>
       </c>
       <c r="B30" t="n">
         <v>101109</v>
@@ -3678,13 +3678,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>351891</v>
+        <v>352092</v>
       </c>
       <c r="R30" t="n">
-        <v>6625317</v>
+        <v>6624985</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130080734</v>
+        <v>130080729</v>
       </c>
       <c r="B31" t="n">
         <v>101109</v>
@@ -3784,13 +3784,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>352092</v>
+        <v>351891</v>
       </c>
       <c r="R31" t="n">
-        <v>6624985</v>
+        <v>6625317</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130080695</v>
+        <v>130080686</v>
       </c>
       <c r="B36" t="n">
         <v>101109</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>351845</v>
+        <v>352054</v>
       </c>
       <c r="R36" t="n">
-        <v>6625269</v>
+        <v>6625054</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130080684</v>
+        <v>130080653</v>
       </c>
       <c r="B37" t="n">
         <v>101109</v>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>352014</v>
+        <v>351849</v>
       </c>
       <c r="R37" t="n">
-        <v>6625206</v>
+        <v>6625259</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4491,7 +4491,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130080686</v>
+        <v>130080695</v>
       </c>
       <c r="B38" t="n">
         <v>101109</v>
@@ -4526,10 +4526,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>352054</v>
+        <v>351845</v>
       </c>
       <c r="R38" t="n">
-        <v>6625054</v>
+        <v>6625269</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4597,7 +4597,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130080653</v>
+        <v>130080684</v>
       </c>
       <c r="B39" t="n">
         <v>101109</v>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>351849</v>
+        <v>352014</v>
       </c>
       <c r="R39" t="n">
-        <v>6625259</v>
+        <v>6625206</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130080706</v>
+        <v>130080703</v>
       </c>
       <c r="B41" t="n">
-        <v>101109</v>
+        <v>40211</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>214803</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>351862</v>
+        <v>351947</v>
       </c>
       <c r="R41" t="n">
-        <v>6625305</v>
+        <v>6625286</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4915,10 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130080703</v>
+        <v>130080706</v>
       </c>
       <c r="B42" t="n">
-        <v>40211</v>
+        <v>101109</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>214803</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>351947</v>
+        <v>351862</v>
       </c>
       <c r="R42" t="n">
-        <v>6625286</v>
+        <v>6625305</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5127,32 +5127,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130080707</v>
+        <v>130080705</v>
       </c>
       <c r="B44" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>351988</v>
+        <v>351964</v>
       </c>
       <c r="R44" t="n">
-        <v>6625206</v>
+        <v>6625310</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130080659</v>
+        <v>130080707</v>
       </c>
       <c r="B45" t="n">
         <v>101109</v>
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>351978</v>
+        <v>351988</v>
       </c>
       <c r="R45" t="n">
-        <v>6625180</v>
+        <v>6625206</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5339,7 +5339,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130080722</v>
+        <v>130080750</v>
       </c>
       <c r="B46" t="n">
         <v>101109</v>
@@ -5368,16 +5368,20 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tostebol 2:1, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>351871</v>
+        <v>352033</v>
       </c>
       <c r="R46" t="n">
-        <v>6625188</v>
+        <v>6625037</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5418,6 +5422,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5445,7 +5450,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130080746</v>
+        <v>130080754</v>
       </c>
       <c r="B47" t="n">
         <v>101109</v>
@@ -5480,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>351961</v>
+        <v>351994</v>
       </c>
       <c r="R47" t="n">
-        <v>6625364</v>
+        <v>6625214</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5551,7 +5556,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130080750</v>
+        <v>130080687</v>
       </c>
       <c r="B48" t="n">
         <v>101109</v>
@@ -5580,20 +5585,16 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tostebol 2:1, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>352033</v>
+        <v>352063</v>
       </c>
       <c r="R48" t="n">
-        <v>6625037</v>
+        <v>6625046</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5634,7 +5635,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5662,7 +5662,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130080754</v>
+        <v>130080668</v>
       </c>
       <c r="B49" t="n">
         <v>101109</v>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>351994</v>
+        <v>352009</v>
       </c>
       <c r="R49" t="n">
-        <v>6625214</v>
+        <v>6625177</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5768,7 +5768,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130080687</v>
+        <v>130080722</v>
       </c>
       <c r="B50" t="n">
         <v>101109</v>
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>352063</v>
+        <v>351871</v>
       </c>
       <c r="R50" t="n">
-        <v>6625046</v>
+        <v>6625188</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5874,7 +5874,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130080743</v>
+        <v>130080746</v>
       </c>
       <c r="B51" t="n">
         <v>101109</v>
@@ -5909,10 +5909,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>351863</v>
+        <v>351961</v>
       </c>
       <c r="R51" t="n">
-        <v>6625270</v>
+        <v>6625364</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6298,32 +6298,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130080705</v>
+        <v>130080659</v>
       </c>
       <c r="B55" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6333,13 +6333,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>351964</v>
+        <v>351978</v>
       </c>
       <c r="R55" t="n">
-        <v>6625310</v>
+        <v>6625180</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130080668</v>
+        <v>130080743</v>
       </c>
       <c r="B56" t="n">
         <v>101109</v>
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>352009</v>
+        <v>351863</v>
       </c>
       <c r="R56" t="n">
-        <v>6625177</v>
+        <v>6625270</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6510,10 +6510,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130080735</v>
+        <v>130080731</v>
       </c>
       <c r="B57" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>352060</v>
+        <v>352108</v>
       </c>
       <c r="R57" t="n">
-        <v>6624988</v>
+        <v>6625477</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6616,10 +6616,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130080692</v>
+        <v>130080702</v>
       </c>
       <c r="B58" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6627,21 +6627,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>351814</v>
+        <v>352012</v>
       </c>
       <c r="R58" t="n">
-        <v>6625310</v>
+        <v>6625262</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6828,10 +6828,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130080731</v>
+        <v>130080735</v>
       </c>
       <c r="B60" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6839,21 +6839,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>352108</v>
+        <v>352060</v>
       </c>
       <c r="R60" t="n">
-        <v>6625477</v>
+        <v>6624988</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6934,10 +6934,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130080702</v>
+        <v>130080692</v>
       </c>
       <c r="B61" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6945,21 +6945,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6969,10 +6969,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>352012</v>
+        <v>351814</v>
       </c>
       <c r="R61" t="n">
-        <v>6625262</v>
+        <v>6625310</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130080661</v>
+        <v>130080720</v>
       </c>
       <c r="B62" t="n">
-        <v>101109</v>
+        <v>57019</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7051,21 +7051,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>102613</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7075,13 +7075,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>351899</v>
+        <v>352012</v>
       </c>
       <c r="R62" t="n">
-        <v>6625315</v>
+        <v>6625216</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130080648</v>
+        <v>130080661</v>
       </c>
       <c r="B63" t="n">
         <v>101109</v>
@@ -7181,13 +7181,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>351888</v>
+        <v>351899</v>
       </c>
       <c r="R63" t="n">
-        <v>6625110</v>
+        <v>6625315</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7252,10 +7252,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130080720</v>
+        <v>130080648</v>
       </c>
       <c r="B64" t="n">
-        <v>57019</v>
+        <v>101109</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7263,21 +7263,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102613</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7287,10 +7287,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>352012</v>
+        <v>351888</v>
       </c>
       <c r="R64" t="n">
-        <v>6625216</v>
+        <v>6625110</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7358,7 +7358,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130080683</v>
+        <v>130080682</v>
       </c>
       <c r="B65" t="n">
         <v>101109</v>
@@ -7393,10 +7393,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>351950</v>
+        <v>352070</v>
       </c>
       <c r="R65" t="n">
-        <v>6624962</v>
+        <v>6624978</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7570,32 +7570,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130080732</v>
+        <v>130080683</v>
       </c>
       <c r="B67" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7605,10 +7605,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>351949</v>
+        <v>351950</v>
       </c>
       <c r="R67" t="n">
-        <v>6625336</v>
+        <v>6624962</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7676,32 +7676,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130080682</v>
+        <v>130080732</v>
       </c>
       <c r="B68" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7711,10 +7711,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>352070</v>
+        <v>351949</v>
       </c>
       <c r="R68" t="n">
-        <v>6624978</v>
+        <v>6625336</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7782,7 +7782,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130080677</v>
+        <v>130080744</v>
       </c>
       <c r="B69" t="n">
         <v>101109</v>
@@ -7817,13 +7817,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>351993</v>
+        <v>352017</v>
       </c>
       <c r="R69" t="n">
-        <v>6625176</v>
+        <v>6625252</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130080744</v>
+        <v>130080677</v>
       </c>
       <c r="B70" t="n">
         <v>101109</v>
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>352017</v>
+        <v>351993</v>
       </c>
       <c r="R70" t="n">
-        <v>6625252</v>
+        <v>6625176</v>
       </c>
       <c r="S70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7994,10 +7994,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130080753</v>
+        <v>130080688</v>
       </c>
       <c r="B71" t="n">
-        <v>57823</v>
+        <v>93048</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8005,21 +8005,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>351938</v>
+        <v>351946</v>
       </c>
       <c r="R71" t="n">
-        <v>6625338</v>
+        <v>6625322</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8100,32 +8100,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130080688</v>
+        <v>130080658</v>
       </c>
       <c r="B72" t="n">
-        <v>93048</v>
+        <v>80320</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5966</v>
+        <v>6463</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8135,13 +8135,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>351946</v>
+        <v>352098</v>
       </c>
       <c r="R72" t="n">
-        <v>6625322</v>
+        <v>6625401</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8206,32 +8206,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130080658</v>
+        <v>130080753</v>
       </c>
       <c r="B73" t="n">
-        <v>80320</v>
+        <v>57823</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8241,13 +8241,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>352098</v>
+        <v>351938</v>
       </c>
       <c r="R73" t="n">
-        <v>6625401</v>
+        <v>6625338</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130080643</v>
+        <v>130080649</v>
       </c>
       <c r="B74" t="n">
         <v>101109</v>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>352061</v>
+        <v>351813</v>
       </c>
       <c r="R74" t="n">
-        <v>6625058</v>
+        <v>6625308</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8418,7 +8418,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130080680</v>
+        <v>130080690</v>
       </c>
       <c r="B75" t="n">
         <v>101109</v>
@@ -8453,13 +8453,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>351923</v>
+        <v>351880</v>
       </c>
       <c r="R75" t="n">
-        <v>6625280</v>
+        <v>6625196</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130080649</v>
+        <v>130080680</v>
       </c>
       <c r="B76" t="n">
         <v>101109</v>
@@ -8559,13 +8559,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>351813</v>
+        <v>351923</v>
       </c>
       <c r="R76" t="n">
-        <v>6625308</v>
+        <v>6625280</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130080690</v>
+        <v>130080643</v>
       </c>
       <c r="B77" t="n">
         <v>101109</v>
@@ -8665,13 +8665,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>351880</v>
+        <v>352061</v>
       </c>
       <c r="R77" t="n">
-        <v>6625196</v>
+        <v>6625058</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8948,10 +8948,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130080675</v>
+        <v>130080698</v>
       </c>
       <c r="B80" t="n">
-        <v>101109</v>
+        <v>4773</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8959,21 +8959,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8983,10 +8983,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>352078</v>
+        <v>351986</v>
       </c>
       <c r="R80" t="n">
-        <v>6624994</v>
+        <v>6625378</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9054,32 +9054,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130080724</v>
+        <v>130080652</v>
       </c>
       <c r="B81" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9089,10 +9089,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>352010</v>
+        <v>351953</v>
       </c>
       <c r="R81" t="n">
-        <v>6625223</v>
+        <v>6625320</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9160,32 +9160,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130080652</v>
+        <v>130080675</v>
       </c>
       <c r="B82" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>351953</v>
+        <v>352078</v>
       </c>
       <c r="R82" t="n">
-        <v>6625320</v>
+        <v>6624994</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9372,10 +9372,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130080698</v>
+        <v>130080724</v>
       </c>
       <c r="B84" t="n">
-        <v>4773</v>
+        <v>101109</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9383,21 +9383,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9407,10 +9407,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>351986</v>
+        <v>352010</v>
       </c>
       <c r="R84" t="n">
-        <v>6625378</v>
+        <v>6625223</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>

--- a/artfynd/A 34970-2025 artfynd.xlsx
+++ b/artfynd/A 34970-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130080714</v>
+        <v>130080721</v>
       </c>
       <c r="B2" t="n">
-        <v>101109</v>
+        <v>91692</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>352013</v>
+        <v>351857</v>
       </c>
       <c r="R2" t="n">
-        <v>6625233</v>
+        <v>6625260</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130080721</v>
+        <v>130080714</v>
       </c>
       <c r="B3" t="n">
-        <v>91692</v>
+        <v>101109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>351857</v>
+        <v>352013</v>
       </c>
       <c r="R3" t="n">
-        <v>6625260</v>
+        <v>6625233</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130080737</v>
+        <v>130080644</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>4773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>351971</v>
+        <v>352049</v>
       </c>
       <c r="R7" t="n">
-        <v>6625428</v>
+        <v>6625465</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130080644</v>
+        <v>130080737</v>
       </c>
       <c r="B8" t="n">
-        <v>4773</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>352049</v>
+        <v>351971</v>
       </c>
       <c r="R8" t="n">
-        <v>6625465</v>
+        <v>6625428</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130080742</v>
+        <v>130080665</v>
       </c>
       <c r="B13" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>352129</v>
+        <v>351806</v>
       </c>
       <c r="R13" t="n">
-        <v>6625324</v>
+        <v>6625305</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130080672</v>
+        <v>130080730</v>
       </c>
       <c r="B14" t="n">
-        <v>8440</v>
+        <v>101109</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>351844</v>
+        <v>351959</v>
       </c>
       <c r="R14" t="n">
-        <v>6625206</v>
+        <v>6625368</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130080665</v>
+        <v>130080672</v>
       </c>
       <c r="B15" t="n">
-        <v>101109</v>
+        <v>8440</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,21 +2064,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>351806</v>
+        <v>351844</v>
       </c>
       <c r="R15" t="n">
-        <v>6625305</v>
+        <v>6625206</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130080730</v>
+        <v>130080742</v>
       </c>
       <c r="B16" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2170,21 +2170,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>351959</v>
+        <v>352129</v>
       </c>
       <c r="R16" t="n">
-        <v>6625368</v>
+        <v>6625324</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130080650</v>
+        <v>130080691</v>
       </c>
       <c r="B17" t="n">
-        <v>8440</v>
+        <v>101109</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>351899</v>
+        <v>351862</v>
       </c>
       <c r="R17" t="n">
-        <v>6624970</v>
+        <v>6625186</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130080691</v>
+        <v>130080733</v>
       </c>
       <c r="B18" t="n">
         <v>101109</v>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>351862</v>
+        <v>352048</v>
       </c>
       <c r="R18" t="n">
-        <v>6625186</v>
+        <v>6624973</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130080733</v>
+        <v>130080660</v>
       </c>
       <c r="B19" t="n">
         <v>101109</v>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>352048</v>
+        <v>351973</v>
       </c>
       <c r="R19" t="n">
-        <v>6624973</v>
+        <v>6625359</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130080660</v>
+        <v>130080650</v>
       </c>
       <c r="B20" t="n">
-        <v>101109</v>
+        <v>8440</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2618,13 +2618,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>351973</v>
+        <v>351899</v>
       </c>
       <c r="R20" t="n">
-        <v>6625359</v>
+        <v>6624970</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2689,32 +2689,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130080704</v>
+        <v>130080718</v>
       </c>
       <c r="B21" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>352045</v>
+        <v>351953</v>
       </c>
       <c r="R21" t="n">
-        <v>6625019</v>
+        <v>6625332</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130080697</v>
+        <v>130080704</v>
       </c>
       <c r="B22" t="n">
         <v>101109</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>352047</v>
+        <v>352045</v>
       </c>
       <c r="R22" t="n">
-        <v>6625052</v>
+        <v>6625019</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3219,32 +3219,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130080718</v>
+        <v>130080697</v>
       </c>
       <c r="B26" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>351953</v>
+        <v>352047</v>
       </c>
       <c r="R26" t="n">
-        <v>6625332</v>
+        <v>6625052</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130080709</v>
+        <v>130080686</v>
       </c>
       <c r="B34" t="n">
-        <v>91158</v>
+        <v>101109</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>351843</v>
+        <v>352054</v>
       </c>
       <c r="R34" t="n">
-        <v>6625177</v>
+        <v>6625054</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4173,32 +4173,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130080727</v>
+        <v>130080653</v>
       </c>
       <c r="B35" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>351974</v>
+        <v>351849</v>
       </c>
       <c r="R35" t="n">
-        <v>6625448</v>
+        <v>6625259</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130080686</v>
+        <v>130080695</v>
       </c>
       <c r="B36" t="n">
         <v>101109</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>352054</v>
+        <v>351845</v>
       </c>
       <c r="R36" t="n">
-        <v>6625054</v>
+        <v>6625269</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130080653</v>
+        <v>130080684</v>
       </c>
       <c r="B37" t="n">
         <v>101109</v>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>351849</v>
+        <v>352014</v>
       </c>
       <c r="R37" t="n">
-        <v>6625259</v>
+        <v>6625206</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130080695</v>
+        <v>130080709</v>
       </c>
       <c r="B38" t="n">
-        <v>101109</v>
+        <v>91158</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4502,21 +4502,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4526,10 +4526,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>351845</v>
+        <v>351843</v>
       </c>
       <c r="R38" t="n">
-        <v>6625269</v>
+        <v>6625177</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4597,32 +4597,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130080684</v>
+        <v>130080727</v>
       </c>
       <c r="B39" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4632,13 +4632,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>352014</v>
+        <v>351974</v>
       </c>
       <c r="R39" t="n">
-        <v>6625206</v>
+        <v>6625448</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130080703</v>
+        <v>130080706</v>
       </c>
       <c r="B41" t="n">
-        <v>40211</v>
+        <v>101109</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>214803</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>351947</v>
+        <v>351862</v>
       </c>
       <c r="R41" t="n">
-        <v>6625286</v>
+        <v>6625305</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4915,10 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130080706</v>
+        <v>130080689</v>
       </c>
       <c r="B42" t="n">
-        <v>101109</v>
+        <v>80153</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>6441</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>351862</v>
+        <v>352000</v>
       </c>
       <c r="R42" t="n">
-        <v>6625305</v>
+        <v>6625332</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5021,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130080689</v>
+        <v>130080703</v>
       </c>
       <c r="B43" t="n">
-        <v>80153</v>
+        <v>40211</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6441</v>
+        <v>214803</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>352000</v>
+        <v>351947</v>
       </c>
       <c r="R43" t="n">
-        <v>6625332</v>
+        <v>6625286</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5127,32 +5127,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130080705</v>
+        <v>130080754</v>
       </c>
       <c r="B44" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>351964</v>
+        <v>351994</v>
       </c>
       <c r="R44" t="n">
-        <v>6625310</v>
+        <v>6625214</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130080754</v>
+        <v>130080687</v>
       </c>
       <c r="B47" t="n">
         <v>101109</v>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>351994</v>
+        <v>352063</v>
       </c>
       <c r="R47" t="n">
-        <v>6625214</v>
+        <v>6625046</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5556,7 +5556,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130080687</v>
+        <v>130080659</v>
       </c>
       <c r="B48" t="n">
         <v>101109</v>
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>352063</v>
+        <v>351978</v>
       </c>
       <c r="R48" t="n">
-        <v>6625046</v>
+        <v>6625180</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5980,7 +5980,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130080674</v>
+        <v>130080743</v>
       </c>
       <c r="B52" t="n">
         <v>101109</v>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>352086</v>
+        <v>351863</v>
       </c>
       <c r="R52" t="n">
-        <v>6624991</v>
+        <v>6625270</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130080749</v>
+        <v>130080674</v>
       </c>
       <c r="B53" t="n">
         <v>101109</v>
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>352067</v>
+        <v>352086</v>
       </c>
       <c r="R53" t="n">
-        <v>6624994</v>
+        <v>6624991</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6192,7 +6192,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130080719</v>
+        <v>130080749</v>
       </c>
       <c r="B54" t="n">
         <v>101109</v>
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>351983</v>
+        <v>352067</v>
       </c>
       <c r="R54" t="n">
-        <v>6625356</v>
+        <v>6624994</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6298,7 +6298,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130080659</v>
+        <v>130080719</v>
       </c>
       <c r="B55" t="n">
         <v>101109</v>
@@ -6333,10 +6333,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>351978</v>
+        <v>351983</v>
       </c>
       <c r="R55" t="n">
-        <v>6625180</v>
+        <v>6625356</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6404,32 +6404,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130080743</v>
+        <v>130080705</v>
       </c>
       <c r="B56" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6439,13 +6439,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>351863</v>
+        <v>351964</v>
       </c>
       <c r="R56" t="n">
-        <v>6625270</v>
+        <v>6625310</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6510,10 +6510,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130080731</v>
+        <v>130080700</v>
       </c>
       <c r="B57" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6545,13 +6545,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>352108</v>
+        <v>351954</v>
       </c>
       <c r="R57" t="n">
-        <v>6625477</v>
+        <v>6625185</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6616,10 +6616,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130080702</v>
+        <v>130080735</v>
       </c>
       <c r="B58" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6627,21 +6627,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>352012</v>
+        <v>352060</v>
       </c>
       <c r="R58" t="n">
-        <v>6625262</v>
+        <v>6624988</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6722,7 +6722,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130080700</v>
+        <v>130080692</v>
       </c>
       <c r="B59" t="n">
         <v>101109</v>
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>351954</v>
+        <v>351814</v>
       </c>
       <c r="R59" t="n">
-        <v>6625185</v>
+        <v>6625310</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6828,10 +6828,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130080735</v>
+        <v>130080702</v>
       </c>
       <c r="B60" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6839,21 +6839,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>352060</v>
+        <v>352012</v>
       </c>
       <c r="R60" t="n">
-        <v>6624988</v>
+        <v>6625262</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6934,10 +6934,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130080692</v>
+        <v>130080731</v>
       </c>
       <c r="B61" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6945,21 +6945,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6969,10 +6969,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>351814</v>
+        <v>352108</v>
       </c>
       <c r="R61" t="n">
-        <v>6625310</v>
+        <v>6625477</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7358,32 +7358,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130080682</v>
+        <v>130080732</v>
       </c>
       <c r="B65" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7393,10 +7393,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>352070</v>
+        <v>351949</v>
       </c>
       <c r="R65" t="n">
-        <v>6624978</v>
+        <v>6625336</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7676,32 +7676,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130080732</v>
+        <v>130080682</v>
       </c>
       <c r="B68" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7711,10 +7711,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>351949</v>
+        <v>352070</v>
       </c>
       <c r="R68" t="n">
-        <v>6625336</v>
+        <v>6624978</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7782,32 +7782,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130080744</v>
+        <v>130080753</v>
       </c>
       <c r="B69" t="n">
-        <v>101109</v>
+        <v>57823</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7817,13 +7817,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>352017</v>
+        <v>351938</v>
       </c>
       <c r="R69" t="n">
-        <v>6625252</v>
+        <v>6625338</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130080677</v>
+        <v>130080744</v>
       </c>
       <c r="B70" t="n">
         <v>101109</v>
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>351993</v>
+        <v>352017</v>
       </c>
       <c r="R70" t="n">
-        <v>6625176</v>
+        <v>6625252</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7994,32 +7994,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130080688</v>
+        <v>130080677</v>
       </c>
       <c r="B71" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>351946</v>
+        <v>351993</v>
       </c>
       <c r="R71" t="n">
-        <v>6625322</v>
+        <v>6625176</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8100,32 +8100,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130080658</v>
+        <v>130080688</v>
       </c>
       <c r="B72" t="n">
-        <v>80320</v>
+        <v>93048</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6463</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8135,13 +8135,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>352098</v>
+        <v>351946</v>
       </c>
       <c r="R72" t="n">
-        <v>6625401</v>
+        <v>6625322</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8206,32 +8206,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130080753</v>
+        <v>130080658</v>
       </c>
       <c r="B73" t="n">
-        <v>57823</v>
+        <v>80320</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8241,13 +8241,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>351938</v>
+        <v>352098</v>
       </c>
       <c r="R73" t="n">
-        <v>6625338</v>
+        <v>6625401</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130080649</v>
+        <v>130080643</v>
       </c>
       <c r="B74" t="n">
         <v>101109</v>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>351813</v>
+        <v>352061</v>
       </c>
       <c r="R74" t="n">
-        <v>6625308</v>
+        <v>6625058</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8418,7 +8418,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130080690</v>
+        <v>130080649</v>
       </c>
       <c r="B75" t="n">
         <v>101109</v>
@@ -8453,13 +8453,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>351880</v>
+        <v>351813</v>
       </c>
       <c r="R75" t="n">
-        <v>6625196</v>
+        <v>6625308</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130080680</v>
+        <v>130080690</v>
       </c>
       <c r="B76" t="n">
         <v>101109</v>
@@ -8559,13 +8559,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>351923</v>
+        <v>351880</v>
       </c>
       <c r="R76" t="n">
-        <v>6625280</v>
+        <v>6625196</v>
       </c>
       <c r="S76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130080643</v>
+        <v>130080680</v>
       </c>
       <c r="B77" t="n">
         <v>101109</v>
@@ -8665,13 +8665,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>352061</v>
+        <v>351923</v>
       </c>
       <c r="R77" t="n">
-        <v>6625058</v>
+        <v>6625280</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8736,32 +8736,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130080711</v>
+        <v>130080748</v>
       </c>
       <c r="B78" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8771,10 +8771,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>351948</v>
+        <v>351968</v>
       </c>
       <c r="R78" t="n">
-        <v>6625339</v>
+        <v>6625362</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8842,32 +8842,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130080748</v>
+        <v>130080711</v>
       </c>
       <c r="B79" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8877,10 +8877,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>351968</v>
+        <v>351948</v>
       </c>
       <c r="R79" t="n">
-        <v>6625362</v>
+        <v>6625339</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8948,10 +8948,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130080698</v>
+        <v>130080675</v>
       </c>
       <c r="B80" t="n">
-        <v>4773</v>
+        <v>101109</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8959,21 +8959,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8983,10 +8983,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>351986</v>
+        <v>352078</v>
       </c>
       <c r="R80" t="n">
-        <v>6625378</v>
+        <v>6624994</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9054,32 +9054,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130080652</v>
+        <v>130080747</v>
       </c>
       <c r="B81" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9089,10 +9089,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>351953</v>
+        <v>351963</v>
       </c>
       <c r="R81" t="n">
-        <v>6625320</v>
+        <v>6625354</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9160,7 +9160,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130080675</v>
+        <v>130080724</v>
       </c>
       <c r="B82" t="n">
         <v>101109</v>
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>352078</v>
+        <v>352010</v>
       </c>
       <c r="R82" t="n">
-        <v>6624994</v>
+        <v>6625223</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9266,32 +9266,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130080747</v>
+        <v>130080652</v>
       </c>
       <c r="B83" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>351963</v>
+        <v>351953</v>
       </c>
       <c r="R83" t="n">
-        <v>6625354</v>
+        <v>6625320</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9372,10 +9372,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130080724</v>
+        <v>130080698</v>
       </c>
       <c r="B84" t="n">
-        <v>101109</v>
+        <v>4773</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9383,21 +9383,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9407,10 +9407,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>352010</v>
+        <v>351986</v>
       </c>
       <c r="R84" t="n">
-        <v>6625223</v>
+        <v>6625378</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>

--- a/artfynd/A 34970-2025 artfynd.xlsx
+++ b/artfynd/A 34970-2025 artfynd.xlsx
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130080644</v>
+        <v>130080737</v>
       </c>
       <c r="B7" t="n">
-        <v>4773</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>352049</v>
+        <v>351971</v>
       </c>
       <c r="R7" t="n">
-        <v>6625465</v>
+        <v>6625428</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130080737</v>
+        <v>130080715</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>5197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>351971</v>
+        <v>352047</v>
       </c>
       <c r="R8" t="n">
-        <v>6625428</v>
+        <v>6625255</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130080715</v>
+        <v>130080693</v>
       </c>
       <c r="B9" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>352047</v>
+        <v>351872</v>
       </c>
       <c r="R9" t="n">
-        <v>6625255</v>
+        <v>6625323</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130080693</v>
+        <v>130080678</v>
       </c>
       <c r="B10" t="n">
         <v>101109</v>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>351872</v>
+        <v>351989</v>
       </c>
       <c r="R10" t="n">
-        <v>6625323</v>
+        <v>6625211</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130080678</v>
+        <v>130080664</v>
       </c>
       <c r="B11" t="n">
         <v>101109</v>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>351989</v>
+        <v>352009</v>
       </c>
       <c r="R11" t="n">
-        <v>6625211</v>
+        <v>6625188</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130080664</v>
+        <v>130080644</v>
       </c>
       <c r="B12" t="n">
-        <v>101109</v>
+        <v>4773</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>352009</v>
+        <v>352049</v>
       </c>
       <c r="R12" t="n">
-        <v>6625188</v>
+        <v>6625465</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130080665</v>
+        <v>130080672</v>
       </c>
       <c r="B13" t="n">
-        <v>101109</v>
+        <v>8440</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>351806</v>
+        <v>351844</v>
       </c>
       <c r="R13" t="n">
-        <v>6625305</v>
+        <v>6625206</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130080730</v>
+        <v>130080742</v>
       </c>
       <c r="B14" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>351959</v>
+        <v>352129</v>
       </c>
       <c r="R14" t="n">
-        <v>6625368</v>
+        <v>6625324</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130080672</v>
+        <v>130080665</v>
       </c>
       <c r="B15" t="n">
-        <v>8440</v>
+        <v>101109</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,21 +2064,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>351844</v>
+        <v>351806</v>
       </c>
       <c r="R15" t="n">
-        <v>6625206</v>
+        <v>6625305</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130080742</v>
+        <v>130080730</v>
       </c>
       <c r="B16" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2170,21 +2170,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>352129</v>
+        <v>351959</v>
       </c>
       <c r="R16" t="n">
-        <v>6625324</v>
+        <v>6625368</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2901,7 +2901,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130080673</v>
+        <v>130080697</v>
       </c>
       <c r="B23" t="n">
         <v>101109</v>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>351941</v>
+        <v>352047</v>
       </c>
       <c r="R23" t="n">
-        <v>6625194</v>
+        <v>6625052</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3007,7 +3007,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130080725</v>
+        <v>130080673</v>
       </c>
       <c r="B24" t="n">
         <v>101109</v>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>351884</v>
+        <v>351941</v>
       </c>
       <c r="R24" t="n">
-        <v>6625119</v>
+        <v>6625194</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3113,7 +3113,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130080716</v>
+        <v>130080725</v>
       </c>
       <c r="B25" t="n">
         <v>101109</v>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>352027</v>
+        <v>351884</v>
       </c>
       <c r="R25" t="n">
-        <v>6625029</v>
+        <v>6625119</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130080697</v>
+        <v>130080716</v>
       </c>
       <c r="B26" t="n">
         <v>101109</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>352047</v>
+        <v>352027</v>
       </c>
       <c r="R26" t="n">
-        <v>6625052</v>
+        <v>6625029</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130080686</v>
+        <v>130080709</v>
       </c>
       <c r="B34" t="n">
-        <v>101109</v>
+        <v>91158</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>352054</v>
+        <v>351843</v>
       </c>
       <c r="R34" t="n">
-        <v>6625054</v>
+        <v>6625177</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130080653</v>
+        <v>130080686</v>
       </c>
       <c r="B35" t="n">
         <v>101109</v>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>351849</v>
+        <v>352054</v>
       </c>
       <c r="R35" t="n">
-        <v>6625259</v>
+        <v>6625054</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130080695</v>
+        <v>130080653</v>
       </c>
       <c r="B36" t="n">
         <v>101109</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>351845</v>
+        <v>351849</v>
       </c>
       <c r="R36" t="n">
-        <v>6625269</v>
+        <v>6625259</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130080684</v>
+        <v>130080695</v>
       </c>
       <c r="B37" t="n">
         <v>101109</v>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>352014</v>
+        <v>351845</v>
       </c>
       <c r="R37" t="n">
-        <v>6625206</v>
+        <v>6625269</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130080709</v>
+        <v>130080684</v>
       </c>
       <c r="B38" t="n">
-        <v>91158</v>
+        <v>101109</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4502,21 +4502,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4526,10 +4526,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>351843</v>
+        <v>352014</v>
       </c>
       <c r="R38" t="n">
-        <v>6625177</v>
+        <v>6625206</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4597,32 +4597,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130080727</v>
+        <v>130080694</v>
       </c>
       <c r="B39" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4632,13 +4632,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>351974</v>
+        <v>352047</v>
       </c>
       <c r="R39" t="n">
-        <v>6625448</v>
+        <v>6624983</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4703,32 +4703,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130080694</v>
+        <v>130080727</v>
       </c>
       <c r="B40" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4738,13 +4738,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>352047</v>
+        <v>351974</v>
       </c>
       <c r="R40" t="n">
-        <v>6624983</v>
+        <v>6625448</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130080706</v>
+        <v>130080689</v>
       </c>
       <c r="B41" t="n">
-        <v>101109</v>
+        <v>80153</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>6441</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>351862</v>
+        <v>352000</v>
       </c>
       <c r="R41" t="n">
-        <v>6625305</v>
+        <v>6625332</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4915,10 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130080689</v>
+        <v>130080706</v>
       </c>
       <c r="B42" t="n">
-        <v>80153</v>
+        <v>101109</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6441</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>352000</v>
+        <v>351862</v>
       </c>
       <c r="R42" t="n">
-        <v>6625332</v>
+        <v>6625305</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5127,32 +5127,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130080754</v>
+        <v>130080705</v>
       </c>
       <c r="B44" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>351994</v>
+        <v>351964</v>
       </c>
       <c r="R44" t="n">
-        <v>6625214</v>
+        <v>6625310</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130080687</v>
+        <v>130080754</v>
       </c>
       <c r="B47" t="n">
         <v>101109</v>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>352063</v>
+        <v>351994</v>
       </c>
       <c r="R47" t="n">
-        <v>6625046</v>
+        <v>6625214</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5556,7 +5556,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130080659</v>
+        <v>130080687</v>
       </c>
       <c r="B48" t="n">
         <v>101109</v>
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>351978</v>
+        <v>352063</v>
       </c>
       <c r="R48" t="n">
-        <v>6625180</v>
+        <v>6625046</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5662,7 +5662,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130080668</v>
+        <v>130080659</v>
       </c>
       <c r="B49" t="n">
         <v>101109</v>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>352009</v>
+        <v>351978</v>
       </c>
       <c r="R49" t="n">
-        <v>6625177</v>
+        <v>6625180</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5768,7 +5768,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130080722</v>
+        <v>130080668</v>
       </c>
       <c r="B50" t="n">
         <v>101109</v>
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>351871</v>
+        <v>352009</v>
       </c>
       <c r="R50" t="n">
-        <v>6625188</v>
+        <v>6625177</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5874,7 +5874,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130080746</v>
+        <v>130080722</v>
       </c>
       <c r="B51" t="n">
         <v>101109</v>
@@ -5909,10 +5909,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>351961</v>
+        <v>351871</v>
       </c>
       <c r="R51" t="n">
-        <v>6625364</v>
+        <v>6625188</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5980,7 +5980,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130080743</v>
+        <v>130080746</v>
       </c>
       <c r="B52" t="n">
         <v>101109</v>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>351863</v>
+        <v>351961</v>
       </c>
       <c r="R52" t="n">
-        <v>6625270</v>
+        <v>6625364</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130080674</v>
+        <v>130080743</v>
       </c>
       <c r="B53" t="n">
         <v>101109</v>
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>352086</v>
+        <v>351863</v>
       </c>
       <c r="R53" t="n">
-        <v>6624991</v>
+        <v>6625270</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6192,7 +6192,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130080749</v>
+        <v>130080674</v>
       </c>
       <c r="B54" t="n">
         <v>101109</v>
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>352067</v>
+        <v>352086</v>
       </c>
       <c r="R54" t="n">
-        <v>6624994</v>
+        <v>6624991</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6298,7 +6298,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130080719</v>
+        <v>130080749</v>
       </c>
       <c r="B55" t="n">
         <v>101109</v>
@@ -6333,10 +6333,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>351983</v>
+        <v>352067</v>
       </c>
       <c r="R55" t="n">
-        <v>6625356</v>
+        <v>6624994</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6404,32 +6404,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130080705</v>
+        <v>130080719</v>
       </c>
       <c r="B56" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6439,13 +6439,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>351964</v>
+        <v>351983</v>
       </c>
       <c r="R56" t="n">
-        <v>6625310</v>
+        <v>6625356</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6510,10 +6510,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130080700</v>
+        <v>130080731</v>
       </c>
       <c r="B57" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6545,13 +6545,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>351954</v>
+        <v>352108</v>
       </c>
       <c r="R57" t="n">
-        <v>6625185</v>
+        <v>6625477</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6616,10 +6616,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130080735</v>
+        <v>130080702</v>
       </c>
       <c r="B58" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6627,21 +6627,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>352060</v>
+        <v>352012</v>
       </c>
       <c r="R58" t="n">
-        <v>6624988</v>
+        <v>6625262</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6722,7 +6722,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130080692</v>
+        <v>130080700</v>
       </c>
       <c r="B59" t="n">
         <v>101109</v>
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>351814</v>
+        <v>351954</v>
       </c>
       <c r="R59" t="n">
-        <v>6625310</v>
+        <v>6625185</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6828,10 +6828,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130080702</v>
+        <v>130080735</v>
       </c>
       <c r="B60" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6839,21 +6839,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>352012</v>
+        <v>352060</v>
       </c>
       <c r="R60" t="n">
-        <v>6625262</v>
+        <v>6624988</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6934,10 +6934,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130080731</v>
+        <v>130080692</v>
       </c>
       <c r="B61" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6945,21 +6945,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6969,10 +6969,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>352108</v>
+        <v>351814</v>
       </c>
       <c r="R61" t="n">
-        <v>6625477</v>
+        <v>6625310</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7464,7 +7464,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130080676</v>
+        <v>130080683</v>
       </c>
       <c r="B66" t="n">
         <v>101109</v>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>352034</v>
+        <v>351950</v>
       </c>
       <c r="R66" t="n">
-        <v>6625020</v>
+        <v>6624962</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7570,7 +7570,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130080683</v>
+        <v>130080682</v>
       </c>
       <c r="B67" t="n">
         <v>101109</v>
@@ -7605,10 +7605,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>351950</v>
+        <v>352070</v>
       </c>
       <c r="R67" t="n">
-        <v>6624962</v>
+        <v>6624978</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7676,7 +7676,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130080682</v>
+        <v>130080676</v>
       </c>
       <c r="B68" t="n">
         <v>101109</v>
@@ -7711,10 +7711,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>352070</v>
+        <v>352034</v>
       </c>
       <c r="R68" t="n">
-        <v>6624978</v>
+        <v>6625020</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7782,32 +7782,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130080753</v>
+        <v>130080658</v>
       </c>
       <c r="B69" t="n">
-        <v>57823</v>
+        <v>80320</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7817,13 +7817,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>351938</v>
+        <v>352098</v>
       </c>
       <c r="R69" t="n">
-        <v>6625338</v>
+        <v>6625401</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7888,32 +7888,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130080744</v>
+        <v>130080688</v>
       </c>
       <c r="B70" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>352017</v>
+        <v>351946</v>
       </c>
       <c r="R70" t="n">
-        <v>6625252</v>
+        <v>6625322</v>
       </c>
       <c r="S70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7994,32 +7994,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130080677</v>
+        <v>130080753</v>
       </c>
       <c r="B71" t="n">
-        <v>101109</v>
+        <v>57823</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>351993</v>
+        <v>351938</v>
       </c>
       <c r="R71" t="n">
-        <v>6625176</v>
+        <v>6625338</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8100,32 +8100,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130080688</v>
+        <v>130080744</v>
       </c>
       <c r="B72" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8135,13 +8135,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>351946</v>
+        <v>352017</v>
       </c>
       <c r="R72" t="n">
-        <v>6625322</v>
+        <v>6625252</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8206,10 +8206,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130080658</v>
+        <v>130080677</v>
       </c>
       <c r="B73" t="n">
-        <v>80320</v>
+        <v>101109</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8217,21 +8217,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8241,13 +8241,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>352098</v>
+        <v>351993</v>
       </c>
       <c r="R73" t="n">
-        <v>6625401</v>
+        <v>6625176</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8736,32 +8736,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130080748</v>
+        <v>130080711</v>
       </c>
       <c r="B78" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8771,10 +8771,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>351968</v>
+        <v>351948</v>
       </c>
       <c r="R78" t="n">
-        <v>6625362</v>
+        <v>6625339</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8842,32 +8842,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130080711</v>
+        <v>130080748</v>
       </c>
       <c r="B79" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8877,10 +8877,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>351948</v>
+        <v>351968</v>
       </c>
       <c r="R79" t="n">
-        <v>6625339</v>
+        <v>6625362</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8948,32 +8948,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130080675</v>
+        <v>130080652</v>
       </c>
       <c r="B80" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8983,10 +8983,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>352078</v>
+        <v>351953</v>
       </c>
       <c r="R80" t="n">
-        <v>6624994</v>
+        <v>6625320</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9054,7 +9054,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130080747</v>
+        <v>130080675</v>
       </c>
       <c r="B81" t="n">
         <v>101109</v>
@@ -9089,10 +9089,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>351963</v>
+        <v>352078</v>
       </c>
       <c r="R81" t="n">
-        <v>6625354</v>
+        <v>6624994</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9160,7 +9160,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130080724</v>
+        <v>130080747</v>
       </c>
       <c r="B82" t="n">
         <v>101109</v>
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>352010</v>
+        <v>351963</v>
       </c>
       <c r="R82" t="n">
-        <v>6625223</v>
+        <v>6625354</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9266,32 +9266,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130080652</v>
+        <v>130080724</v>
       </c>
       <c r="B83" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>351953</v>
+        <v>352010</v>
       </c>
       <c r="R83" t="n">
-        <v>6625320</v>
+        <v>6625223</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>

--- a/artfynd/A 34970-2025 artfynd.xlsx
+++ b/artfynd/A 34970-2025 artfynd.xlsx
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130080672</v>
+        <v>130080742</v>
       </c>
       <c r="B13" t="n">
-        <v>8440</v>
+        <v>5197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>351844</v>
+        <v>352129</v>
       </c>
       <c r="R13" t="n">
-        <v>6625206</v>
+        <v>6625324</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130080742</v>
+        <v>130080672</v>
       </c>
       <c r="B14" t="n">
-        <v>5197</v>
+        <v>8440</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>352129</v>
+        <v>351844</v>
       </c>
       <c r="R14" t="n">
-        <v>6625324</v>
+        <v>6625206</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -7994,10 +7994,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130080658</v>
+        <v>130080744</v>
       </c>
       <c r="B71" t="n">
-        <v>80320</v>
+        <v>101109</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8005,21 +8005,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>352098</v>
+        <v>352017</v>
       </c>
       <c r="R71" t="n">
-        <v>6625401</v>
+        <v>6625252</v>
       </c>
       <c r="S71" t="n">
         <v>6</v>
@@ -8100,7 +8100,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130080744</v>
+        <v>130080677</v>
       </c>
       <c r="B72" t="n">
         <v>101109</v>
@@ -8135,13 +8135,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>352017</v>
+        <v>351993</v>
       </c>
       <c r="R72" t="n">
-        <v>6625252</v>
+        <v>6625176</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8206,10 +8206,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130080677</v>
+        <v>130080658</v>
       </c>
       <c r="B73" t="n">
-        <v>101109</v>
+        <v>80320</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8217,21 +8217,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8241,13 +8241,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>351993</v>
+        <v>352098</v>
       </c>
       <c r="R73" t="n">
-        <v>6625176</v>
+        <v>6625401</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>

--- a/artfynd/A 34970-2025 artfynd.xlsx
+++ b/artfynd/A 34970-2025 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130080715</v>
+        <v>130080644</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>4773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>352047</v>
+        <v>352049</v>
       </c>
       <c r="R8" t="n">
-        <v>6625255</v>
+        <v>6625465</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130080693</v>
+        <v>130080678</v>
       </c>
       <c r="B9" t="n">
         <v>101109</v>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>351872</v>
+        <v>351989</v>
       </c>
       <c r="R9" t="n">
-        <v>6625323</v>
+        <v>6625211</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130080664</v>
+        <v>130080715</v>
       </c>
       <c r="B10" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>352009</v>
+        <v>352047</v>
       </c>
       <c r="R10" t="n">
-        <v>6625188</v>
+        <v>6625255</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130080678</v>
+        <v>130080693</v>
       </c>
       <c r="B11" t="n">
         <v>101109</v>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>351989</v>
+        <v>351872</v>
       </c>
       <c r="R11" t="n">
-        <v>6625211</v>
+        <v>6625323</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130080644</v>
+        <v>130080664</v>
       </c>
       <c r="B12" t="n">
-        <v>4773</v>
+        <v>101109</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>352049</v>
+        <v>352009</v>
       </c>
       <c r="R12" t="n">
-        <v>6625465</v>
+        <v>6625188</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2689,32 +2689,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130080704</v>
+        <v>130080718</v>
       </c>
       <c r="B21" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>352045</v>
+        <v>351953</v>
       </c>
       <c r="R21" t="n">
-        <v>6625019</v>
+        <v>6625332</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130080673</v>
+        <v>130080697</v>
       </c>
       <c r="B22" t="n">
         <v>101109</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>351941</v>
+        <v>352047</v>
       </c>
       <c r="R22" t="n">
-        <v>6625194</v>
+        <v>6625052</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2901,7 +2901,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130080725</v>
+        <v>130080704</v>
       </c>
       <c r="B23" t="n">
         <v>101109</v>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>351884</v>
+        <v>352045</v>
       </c>
       <c r="R23" t="n">
-        <v>6625119</v>
+        <v>6625019</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3007,7 +3007,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130080716</v>
+        <v>130080673</v>
       </c>
       <c r="B24" t="n">
         <v>101109</v>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>352027</v>
+        <v>351941</v>
       </c>
       <c r="R24" t="n">
-        <v>6625029</v>
+        <v>6625194</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3113,32 +3113,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130080718</v>
+        <v>130080725</v>
       </c>
       <c r="B25" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>351953</v>
+        <v>351884</v>
       </c>
       <c r="R25" t="n">
-        <v>6625332</v>
+        <v>6625119</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130080697</v>
+        <v>130080716</v>
       </c>
       <c r="B26" t="n">
         <v>101109</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>352047</v>
+        <v>352027</v>
       </c>
       <c r="R26" t="n">
-        <v>6625052</v>
+        <v>6625029</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130080653</v>
+        <v>130080709</v>
       </c>
       <c r="B34" t="n">
-        <v>101109</v>
+        <v>91158</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>351849</v>
+        <v>351843</v>
       </c>
       <c r="R34" t="n">
-        <v>6625259</v>
+        <v>6625177</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4173,32 +4173,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130080695</v>
+        <v>130080727</v>
       </c>
       <c r="B35" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>351845</v>
+        <v>351974</v>
       </c>
       <c r="R35" t="n">
-        <v>6625269</v>
+        <v>6625448</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130080684</v>
+        <v>130080686</v>
       </c>
       <c r="B36" t="n">
         <v>101109</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>352014</v>
+        <v>352054</v>
       </c>
       <c r="R36" t="n">
-        <v>6625206</v>
+        <v>6625054</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130080694</v>
+        <v>130080653</v>
       </c>
       <c r="B37" t="n">
         <v>101109</v>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>352047</v>
+        <v>351849</v>
       </c>
       <c r="R37" t="n">
-        <v>6624983</v>
+        <v>6625259</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4491,7 +4491,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130080686</v>
+        <v>130080695</v>
       </c>
       <c r="B38" t="n">
         <v>101109</v>
@@ -4526,10 +4526,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>352054</v>
+        <v>351845</v>
       </c>
       <c r="R38" t="n">
-        <v>6625054</v>
+        <v>6625269</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4597,32 +4597,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130080727</v>
+        <v>130080684</v>
       </c>
       <c r="B39" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4632,13 +4632,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>351974</v>
+        <v>352014</v>
       </c>
       <c r="R39" t="n">
-        <v>6625448</v>
+        <v>6625206</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4703,10 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130080709</v>
+        <v>130080694</v>
       </c>
       <c r="B40" t="n">
-        <v>91158</v>
+        <v>101109</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4714,21 +4714,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4738,10 +4738,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>351843</v>
+        <v>352047</v>
       </c>
       <c r="R40" t="n">
-        <v>6625177</v>
+        <v>6624983</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>

--- a/artfynd/A 34970-2025 artfynd.xlsx
+++ b/artfynd/A 34970-2025 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130080681</v>
+        <v>130080679</v>
       </c>
       <c r="B5" t="n">
-        <v>80320</v>
+        <v>8440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>352112</v>
+        <v>351893</v>
       </c>
       <c r="R5" t="n">
-        <v>6625411</v>
+        <v>6624978</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130080679</v>
+        <v>130080681</v>
       </c>
       <c r="B6" t="n">
-        <v>8440</v>
+        <v>80320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>351893</v>
+        <v>352112</v>
       </c>
       <c r="R6" t="n">
-        <v>6624978</v>
+        <v>6625411</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130080644</v>
+        <v>130080715</v>
       </c>
       <c r="B8" t="n">
-        <v>4773</v>
+        <v>5197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>352049</v>
+        <v>352047</v>
       </c>
       <c r="R8" t="n">
-        <v>6625465</v>
+        <v>6625255</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130080678</v>
+        <v>130080693</v>
       </c>
       <c r="B9" t="n">
         <v>101109</v>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>351989</v>
+        <v>351872</v>
       </c>
       <c r="R9" t="n">
-        <v>6625211</v>
+        <v>6625323</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130080715</v>
+        <v>130080664</v>
       </c>
       <c r="B10" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>352047</v>
+        <v>352009</v>
       </c>
       <c r="R10" t="n">
-        <v>6625255</v>
+        <v>6625188</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130080693</v>
+        <v>130080678</v>
       </c>
       <c r="B11" t="n">
         <v>101109</v>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>351872</v>
+        <v>351989</v>
       </c>
       <c r="R11" t="n">
-        <v>6625323</v>
+        <v>6625211</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130080664</v>
+        <v>130080644</v>
       </c>
       <c r="B12" t="n">
-        <v>101109</v>
+        <v>4773</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>352009</v>
+        <v>352049</v>
       </c>
       <c r="R12" t="n">
-        <v>6625188</v>
+        <v>6625465</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130080742</v>
+        <v>130080672</v>
       </c>
       <c r="B13" t="n">
-        <v>5197</v>
+        <v>8440</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>352129</v>
+        <v>351844</v>
       </c>
       <c r="R13" t="n">
-        <v>6625324</v>
+        <v>6625206</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130080672</v>
+        <v>130080742</v>
       </c>
       <c r="B14" t="n">
-        <v>8440</v>
+        <v>5197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>351844</v>
+        <v>352129</v>
       </c>
       <c r="R14" t="n">
-        <v>6625206</v>
+        <v>6625324</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130080709</v>
+        <v>130080653</v>
       </c>
       <c r="B34" t="n">
-        <v>91158</v>
+        <v>101109</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>351843</v>
+        <v>351849</v>
       </c>
       <c r="R34" t="n">
-        <v>6625177</v>
+        <v>6625259</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4173,32 +4173,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130080727</v>
+        <v>130080695</v>
       </c>
       <c r="B35" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>351974</v>
+        <v>351845</v>
       </c>
       <c r="R35" t="n">
-        <v>6625448</v>
+        <v>6625269</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130080686</v>
+        <v>130080684</v>
       </c>
       <c r="B36" t="n">
         <v>101109</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>352054</v>
+        <v>352014</v>
       </c>
       <c r="R36" t="n">
-        <v>6625054</v>
+        <v>6625206</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130080653</v>
+        <v>130080694</v>
       </c>
       <c r="B37" t="n">
         <v>101109</v>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>351849</v>
+        <v>352047</v>
       </c>
       <c r="R37" t="n">
-        <v>6625259</v>
+        <v>6624983</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4491,7 +4491,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130080695</v>
+        <v>130080686</v>
       </c>
       <c r="B38" t="n">
         <v>101109</v>
@@ -4526,10 +4526,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>351845</v>
+        <v>352054</v>
       </c>
       <c r="R38" t="n">
-        <v>6625269</v>
+        <v>6625054</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4597,32 +4597,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130080684</v>
+        <v>130080727</v>
       </c>
       <c r="B39" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4632,13 +4632,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>352014</v>
+        <v>351974</v>
       </c>
       <c r="R39" t="n">
-        <v>6625206</v>
+        <v>6625448</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4703,10 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130080694</v>
+        <v>130080709</v>
       </c>
       <c r="B40" t="n">
-        <v>101109</v>
+        <v>91158</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4714,21 +4714,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4738,10 +4738,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>352047</v>
+        <v>351843</v>
       </c>
       <c r="R40" t="n">
-        <v>6624983</v>
+        <v>6625177</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -7994,10 +7994,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130080744</v>
+        <v>130080658</v>
       </c>
       <c r="B71" t="n">
-        <v>101109</v>
+        <v>80320</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8005,21 +8005,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>352017</v>
+        <v>352098</v>
       </c>
       <c r="R71" t="n">
-        <v>6625252</v>
+        <v>6625401</v>
       </c>
       <c r="S71" t="n">
         <v>6</v>
@@ -8100,7 +8100,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130080677</v>
+        <v>130080744</v>
       </c>
       <c r="B72" t="n">
         <v>101109</v>
@@ -8135,13 +8135,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>351993</v>
+        <v>352017</v>
       </c>
       <c r="R72" t="n">
-        <v>6625176</v>
+        <v>6625252</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8206,10 +8206,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130080658</v>
+        <v>130080677</v>
       </c>
       <c r="B73" t="n">
-        <v>80320</v>
+        <v>101109</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8217,21 +8217,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8241,13 +8241,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>352098</v>
+        <v>351993</v>
       </c>
       <c r="R73" t="n">
-        <v>6625401</v>
+        <v>6625176</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8948,32 +8948,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130080698</v>
+        <v>130080652</v>
       </c>
       <c r="B80" t="n">
-        <v>4773</v>
+        <v>93048</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100299</v>
+        <v>5966</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8983,10 +8983,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>351986</v>
+        <v>351953</v>
       </c>
       <c r="R80" t="n">
-        <v>6625378</v>
+        <v>6625320</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9054,10 +9054,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130080724</v>
+        <v>130080698</v>
       </c>
       <c r="B81" t="n">
-        <v>101109</v>
+        <v>4773</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9065,21 +9065,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9089,10 +9089,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>352010</v>
+        <v>351986</v>
       </c>
       <c r="R81" t="n">
-        <v>6625223</v>
+        <v>6625378</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9160,32 +9160,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130080652</v>
+        <v>130080724</v>
       </c>
       <c r="B82" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>351953</v>
+        <v>352010</v>
       </c>
       <c r="R82" t="n">
-        <v>6625320</v>
+        <v>6625223</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
